--- a/KP_Client_FireProtect.xlsx
+++ b/KP_Client_FireProtect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\fireprotect_kp_bot_mvp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B5C9B3-1302-4CB1-B520-0F6E504011CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226FFA60-4AAE-477E-963D-A1D39ABEEF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KP_Client" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="817">
   <si>
     <t>OFERTĂ COMERCIALĂ</t>
   </si>
@@ -2432,12 +2432,6 @@
     <t>Flanșă oțel D250</t>
   </si>
   <si>
-    <t>Sprinkler cu temp. de acționare 57°C, apă fină, cu rozeta în sus</t>
-  </si>
-  <si>
-    <t>Mufă sudată pentru pulverizatoare cu apă fină MП G1/2, l=50 mm</t>
-  </si>
-  <si>
     <t>Țeavă din oțel zincat Ø26,9* 2.6 mm (DN 20)</t>
   </si>
   <si>
@@ -2532,6 +2526,21 @@
   </si>
   <si>
     <t>Suport / colier pentru țeavă DN200</t>
+  </si>
+  <si>
+    <t>Sprinkler cu temp. de acționare 57°C, apă</t>
+  </si>
+  <si>
+    <t>02 МП G1/2, l=50 mm Mufă sudată pentru</t>
+  </si>
+  <si>
+    <t>RO/PDF line</t>
+  </si>
+  <si>
+    <t>Rețeaua de sprinklere</t>
+  </si>
+  <si>
+    <t>titlu / ignoră</t>
   </si>
 </sst>
 </file>
@@ -2798,23 +2807,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2823,6 +2826,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3156,7 +3165,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -3166,7 +3175,7 @@
       <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -3251,7 +3260,7 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="31"/>
@@ -3671,13 +3680,13 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="12">
         <f>SUM(F11:F25)</f>
         <v>135320.625</v>
@@ -3692,7 +3701,7 @@
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B28" s="31"/>
@@ -4112,13 +4121,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
       <c r="F45" s="12">
         <f>SUM(F30:F44)</f>
         <v>0</v>
@@ -4133,7 +4142,7 @@
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="32" t="s">
         <v>20</v>
       </c>
       <c r="B47" s="31"/>
@@ -4553,13 +4562,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
       <c r="F64" s="12">
         <f>SUM(F49:F63)</f>
         <v>56250</v>
@@ -4574,7 +4583,7 @@
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="36" t="s">
+      <c r="A66" s="32" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="31"/>
@@ -4994,13 +5003,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="34"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="34"/>
       <c r="F83" s="12">
         <f>SUM(F68:F82)</f>
         <v>0</v>
@@ -5015,7 +5024,7 @@
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="32" t="s">
         <v>24</v>
       </c>
       <c r="B85" s="31"/>
@@ -5435,13 +5444,13 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="32" t="s">
+      <c r="A102" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="33"/>
-      <c r="C102" s="33"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="33"/>
+      <c r="B102" s="34"/>
+      <c r="C102" s="34"/>
+      <c r="D102" s="34"/>
+      <c r="E102" s="34"/>
       <c r="F102" s="12">
         <f>SUM(F87:F101)</f>
         <v>0</v>
@@ -5456,7 +5465,7 @@
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="36" t="s">
+      <c r="A104" s="32" t="s">
         <v>26</v>
       </c>
       <c r="B104" s="31"/>
@@ -5876,13 +5885,13 @@
       </c>
     </row>
     <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="32" t="s">
+      <c r="A121" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="33"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="33"/>
-      <c r="E121" s="33"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="34"/>
       <c r="F121" s="12">
         <f>SUM(F106:F120)</f>
         <v>0</v>
@@ -5897,7 +5906,7 @@
       <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="39" t="s">
+      <c r="A123" s="37" t="s">
         <v>28</v>
       </c>
       <c r="B123" s="31"/>
@@ -5910,7 +5919,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="39" t="s">
+      <c r="A124" s="37" t="s">
         <v>29</v>
       </c>
       <c r="B124" s="31"/>
@@ -5923,13 +5932,13 @@
       </c>
     </row>
     <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="37" t="s">
+      <c r="A125" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B125" s="38"/>
-      <c r="C125" s="38"/>
-      <c r="D125" s="38"/>
-      <c r="E125" s="38"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="36"/>
+      <c r="D125" s="36"/>
+      <c r="E125" s="36"/>
       <c r="F125" s="14">
         <f>F123+F124</f>
         <v>229884.75</v>
@@ -5952,7 +5961,7 @@
       <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="40" t="s">
+      <c r="A128" s="38" t="s">
         <v>31</v>
       </c>
       <c r="B128" s="31"/>
@@ -5965,7 +5974,7 @@
       <c r="A129" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B129" s="35" t="s">
+      <c r="B129" s="30" t="s">
         <v>33</v>
       </c>
       <c r="C129" s="31"/>
@@ -5977,7 +5986,7 @@
       <c r="A130" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="35" t="s">
+      <c r="B130" s="30" t="s">
         <v>35</v>
       </c>
       <c r="C130" s="31"/>
@@ -5989,7 +5998,7 @@
       <c r="A131" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B131" s="35" t="s">
+      <c r="B131" s="30" t="s">
         <v>37</v>
       </c>
       <c r="C131" s="31"/>
@@ -6001,7 +6010,7 @@
       <c r="A132" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B132" s="35" t="s">
+      <c r="B132" s="30" t="s">
         <v>39</v>
       </c>
       <c r="C132" s="31"/>
@@ -6019,6 +6028,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A26:E26"/>
@@ -6034,13 +6050,6 @@
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
@@ -6063,7 +6072,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="39" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="41"/>
@@ -18431,11 +18440,11 @@
     </row>
     <row r="316" spans="1:11">
       <c r="A316" s="22" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B316" s="22"/>
       <c r="C316" s="23" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D316" s="22" t="s">
         <v>69</v>
@@ -18462,11 +18471,11 @@
     </row>
     <row r="317" spans="1:11">
       <c r="A317" s="22" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B317" s="22"/>
       <c r="C317" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D317" s="22" t="s">
         <v>69</v>
@@ -18749,7 +18758,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
@@ -18791,8 +18800,8 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="23" t="s">
-        <v>780</v>
+      <c r="A4" t="s">
+        <v>812</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>47</v>
@@ -18824,14 +18833,14 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A7" s="23" t="s">
-        <v>781</v>
+      <c r="A7" t="s">
+        <v>813</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>340</v>
+      <c r="C7" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -19100,7 +19109,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B32" s="27" t="s">
         <v>398</v>
@@ -19111,7 +19120,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="23" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B33" s="27" t="s">
         <v>398</v>
@@ -19133,10 +19142,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C35" s="23" t="s">
         <v>340</v>
@@ -19144,7 +19153,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>384</v>
@@ -19166,7 +19175,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="23" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>384</v>
@@ -19177,7 +19186,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B39" s="27" t="s">
         <v>426</v>
@@ -19188,7 +19197,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B40" s="27" t="s">
         <v>430</v>
@@ -19199,7 +19208,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B41" s="27" t="s">
         <v>612</v>
@@ -19210,7 +19219,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B42" s="27" t="s">
         <v>613</v>
@@ -19221,7 +19230,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B43" s="27" t="s">
         <v>82</v>
@@ -19232,7 +19241,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B44" s="27" t="s">
         <v>84</v>
@@ -19243,7 +19252,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B45" s="27" t="s">
         <v>86</v>
@@ -19254,7 +19263,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B46" s="27" t="s">
         <v>585</v>
@@ -19265,7 +19274,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B47" s="27" t="s">
         <v>586</v>
@@ -19276,7 +19285,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B48" s="27" t="s">
         <v>125</v>
@@ -19287,7 +19296,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B49" s="27" t="s">
         <v>108</v>
@@ -19298,7 +19307,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B50" s="27" t="s">
         <v>110</v>
@@ -19309,7 +19318,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B51" s="27" t="s">
         <v>112</v>
@@ -19320,7 +19329,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B52" s="27" t="s">
         <v>643</v>
@@ -19331,7 +19340,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B53" s="27" t="s">
         <v>295</v>
@@ -19342,7 +19351,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B54" s="27" t="s">
         <v>297</v>
@@ -19353,7 +19362,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B55" s="27" t="s">
         <v>299</v>
@@ -19364,7 +19373,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B56" s="27" t="s">
         <v>307</v>
@@ -19375,7 +19384,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>309</v>
@@ -19386,10 +19395,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>805</v>
+      </c>
+      <c r="B58" s="27" t="s">
         <v>807</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>809</v>
       </c>
       <c r="C58" s="23" t="s">
         <v>340</v>
@@ -19397,7 +19406,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>265</v>
@@ -19419,7 +19428,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>270</v>
@@ -19437,6 +19446,14 @@
       </c>
       <c r="C62" s="23" t="s">
         <v>340</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>815</v>
+      </c>
+      <c r="C63" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/KP_Client_FireProtect.xlsx
+++ b/KP_Client_FireProtect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\fireprotect_kp_bot_mvp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226FFA60-4AAE-477E-963D-A1D39ABEEF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF807168-BF8C-421D-875A-CBDAF306B4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="822">
   <si>
     <t>OFERTĂ COMERCIALĂ</t>
   </si>
@@ -2541,6 +2541,21 @@
   </si>
   <si>
     <t>titlu / ignoră</t>
+  </si>
+  <si>
+    <t>Mufă sudată pentru pulverizatoare cu apă fină</t>
+  </si>
+  <si>
+    <t>Mufă sudată pentru pulverizatoare</t>
+  </si>
+  <si>
+    <t>МП G1/2 l=50 mm</t>
+  </si>
+  <si>
+    <t>МП G1/2</t>
+  </si>
+  <si>
+    <t>МП G1/2, l=50 mm Mufă sudată pentru pulverizatoare cu apă fină</t>
   </si>
 </sst>
 </file>
@@ -8613,8 +8628,8 @@
   <dimension ref="A1:K325"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
@@ -18442,7 +18457,9 @@
       <c r="A316" s="22" t="s">
         <v>810</v>
       </c>
-      <c r="B316" s="22"/>
+      <c r="B316" s="22" t="s">
+        <v>256</v>
+      </c>
       <c r="C316" s="23" t="s">
         <v>811</v>
       </c>
@@ -18473,7 +18490,9 @@
       <c r="A317" s="22" t="s">
         <v>807</v>
       </c>
-      <c r="B317" s="22"/>
+      <c r="B317" s="22" t="s">
+        <v>256</v>
+      </c>
       <c r="C317" t="s">
         <v>806</v>
       </c>
@@ -18758,7 +18777,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
@@ -18800,143 +18819,133 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>812</v>
+      <c r="A4" s="23" t="s">
+        <v>817</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>340</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C4" s="23"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="23" t="s">
-        <v>337</v>
+        <v>818</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>338</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C5" s="23"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="23" t="s">
-        <v>339</v>
+        <v>819</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A7" t="s">
-        <v>813</v>
+      <c r="C6" s="23"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="23" t="s">
+        <v>820</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="C7" t="s">
-        <v>814</v>
-      </c>
+      <c r="C7" s="23"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="23" t="s">
-        <v>341</v>
+      <c r="A8" t="s">
+        <v>812</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>74</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="23" t="s">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>74</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="23" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="23" t="s">
-        <v>344</v>
+        <v>821</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="23" t="s">
-        <v>345</v>
+        <v>184</v>
+      </c>
+      <c r="C11" s="23"/>
+    </row>
+    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>813</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>72</v>
+        <v>184</v>
+      </c>
+      <c r="C12" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="23" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="23" t="s">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>347</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="23" t="s">
-        <v>90</v>
+        <v>342</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>74</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="23" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>72</v>
@@ -18944,32 +18953,32 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="23" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>347</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="23" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="23" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>347</v>
@@ -18977,98 +18986,98 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="23" t="s">
-        <v>351</v>
+        <v>90</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="23" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>347</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="23" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>72</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="23" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>340</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="23" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="23" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>340</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="23" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="23" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>334</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="23" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>340</v>
@@ -19076,98 +19085,98 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="23" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>239</v>
+        <v>50</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="23" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="23" t="s">
-        <v>399</v>
+        <v>357</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>398</v>
+        <v>228</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>780</v>
+      <c r="A32" s="23" t="s">
+        <v>358</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>398</v>
+        <v>51</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="23" t="s">
-        <v>781</v>
+        <v>359</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>398</v>
+        <v>51</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="23" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>379</v>
+        <v>239</v>
       </c>
       <c r="C34" s="23" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>782</v>
+      <c r="A35" s="23" t="s">
+        <v>361</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>783</v>
+        <v>239</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>784</v>
+      <c r="A36" s="23" t="s">
+        <v>399</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="C36" s="23" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="23" t="s">
-        <v>385</v>
+      <c r="A37" t="s">
+        <v>780</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="C37" s="23" t="s">
         <v>340</v>
@@ -19175,21 +19184,21 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="23" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>786</v>
+      <c r="A39" s="23" t="s">
+        <v>378</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>426</v>
+        <v>379</v>
       </c>
       <c r="C39" s="23" t="s">
         <v>340</v>
@@ -19197,10 +19206,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>430</v>
+        <v>783</v>
       </c>
       <c r="C40" s="23" t="s">
         <v>340</v>
@@ -19208,43 +19217,43 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>612</v>
+        <v>384</v>
       </c>
       <c r="C41" s="23" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>789</v>
+      <c r="A42" s="23" t="s">
+        <v>385</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>613</v>
+        <v>384</v>
       </c>
       <c r="C42" s="23" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>790</v>
+      <c r="A43" s="23" t="s">
+        <v>785</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="C44" s="23" t="s">
         <v>340</v>
@@ -19252,10 +19261,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>86</v>
+        <v>430</v>
       </c>
       <c r="C45" s="23" t="s">
         <v>340</v>
@@ -19263,10 +19272,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="C46" s="23" t="s">
         <v>340</v>
@@ -19274,10 +19283,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="C47" s="23" t="s">
         <v>340</v>
@@ -19285,10 +19294,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="C48" s="23" t="s">
         <v>340</v>
@@ -19296,10 +19305,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C49" s="23" t="s">
         <v>340</v>
@@ -19307,10 +19316,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C50" s="23" t="s">
         <v>340</v>
@@ -19318,10 +19327,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>112</v>
+        <v>585</v>
       </c>
       <c r="C51" s="23" t="s">
         <v>340</v>
@@ -19329,10 +19338,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>643</v>
+        <v>586</v>
       </c>
       <c r="C52" s="23" t="s">
         <v>340</v>
@@ -19340,10 +19349,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>295</v>
+        <v>125</v>
       </c>
       <c r="C53" s="23" t="s">
         <v>340</v>
@@ -19351,10 +19360,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>297</v>
+        <v>108</v>
       </c>
       <c r="C54" s="23" t="s">
         <v>340</v>
@@ -19362,10 +19371,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>299</v>
+        <v>110</v>
       </c>
       <c r="C55" s="23" t="s">
         <v>340</v>
@@ -19373,10 +19382,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>307</v>
+        <v>112</v>
       </c>
       <c r="C56" s="23" t="s">
         <v>340</v>
@@ -19384,10 +19393,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>309</v>
+        <v>643</v>
       </c>
       <c r="C57" s="23" t="s">
         <v>340</v>
@@ -19395,10 +19404,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>807</v>
+        <v>295</v>
       </c>
       <c r="C58" s="23" t="s">
         <v>340</v>
@@ -19406,10 +19415,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="C59" s="23" t="s">
         <v>340</v>
@@ -19417,10 +19426,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>268</v>
+        <v>802</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="C60" s="23" t="s">
         <v>340</v>
@@ -19428,10 +19437,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="C61" s="23" t="s">
         <v>340</v>
@@ -19439,10 +19448,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>264</v>
+        <v>804</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="C62" s="23" t="s">
         <v>340</v>
@@ -19450,9 +19459,64 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>805</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>807</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>808</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>809</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>264</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>815</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C68" t="s">
         <v>816</v>
       </c>
     </row>

--- a/KP_Client_FireProtect.xlsx
+++ b/KP_Client_FireProtect.xlsx
@@ -2822,17 +2822,23 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2841,12 +2847,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3180,7 +3180,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -3190,7 +3190,7 @@
       <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -3275,7 +3275,7 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="36" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="31"/>
@@ -3695,13 +3695,13 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="12">
         <f>SUM(F11:F25)</f>
         <v>135320.625</v>
@@ -3716,7 +3716,7 @@
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B28" s="31"/>
@@ -4136,13 +4136,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
       <c r="F45" s="12">
         <f>SUM(F30:F44)</f>
         <v>0</v>
@@ -4157,7 +4157,7 @@
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B47" s="31"/>
@@ -4577,13 +4577,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="33" t="s">
+      <c r="A64" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="34"/>
-      <c r="C64" s="34"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="33"/>
       <c r="F64" s="12">
         <f>SUM(F49:F63)</f>
         <v>56250</v>
@@ -4598,7 +4598,7 @@
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="36" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="31"/>
@@ -5018,13 +5018,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="33" t="s">
+      <c r="A83" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B83" s="34"/>
-      <c r="C83" s="34"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="34"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="33"/>
       <c r="F83" s="12">
         <f>SUM(F68:F82)</f>
         <v>0</v>
@@ -5039,7 +5039,7 @@
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B85" s="31"/>
@@ -5459,13 +5459,13 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="33" t="s">
+      <c r="A102" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="34"/>
-      <c r="C102" s="34"/>
-      <c r="D102" s="34"/>
-      <c r="E102" s="34"/>
+      <c r="B102" s="33"/>
+      <c r="C102" s="33"/>
+      <c r="D102" s="33"/>
+      <c r="E102" s="33"/>
       <c r="F102" s="12">
         <f>SUM(F87:F101)</f>
         <v>0</v>
@@ -5480,7 +5480,7 @@
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="32" t="s">
+      <c r="A104" s="36" t="s">
         <v>26</v>
       </c>
       <c r="B104" s="31"/>
@@ -5900,13 +5900,13 @@
       </c>
     </row>
     <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="33" t="s">
+      <c r="A121" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="34"/>
-      <c r="C121" s="34"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="34"/>
+      <c r="B121" s="33"/>
+      <c r="C121" s="33"/>
+      <c r="D121" s="33"/>
+      <c r="E121" s="33"/>
       <c r="F121" s="12">
         <f>SUM(F106:F120)</f>
         <v>0</v>
@@ -5921,7 +5921,7 @@
       <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="37" t="s">
+      <c r="A123" s="39" t="s">
         <v>28</v>
       </c>
       <c r="B123" s="31"/>
@@ -5934,7 +5934,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="37" t="s">
+      <c r="A124" s="39" t="s">
         <v>29</v>
       </c>
       <c r="B124" s="31"/>
@@ -5947,13 +5947,13 @@
       </c>
     </row>
     <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="35" t="s">
+      <c r="A125" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B125" s="36"/>
-      <c r="C125" s="36"/>
-      <c r="D125" s="36"/>
-      <c r="E125" s="36"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="38"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="38"/>
       <c r="F125" s="14">
         <f>F123+F124</f>
         <v>229884.75</v>
@@ -5976,7 +5976,7 @@
       <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="38" t="s">
+      <c r="A128" s="40" t="s">
         <v>31</v>
       </c>
       <c r="B128" s="31"/>
@@ -5989,7 +5989,7 @@
       <c r="A129" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B129" s="30" t="s">
+      <c r="B129" s="35" t="s">
         <v>33</v>
       </c>
       <c r="C129" s="31"/>
@@ -6001,7 +6001,7 @@
       <c r="A130" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="30" t="s">
+      <c r="B130" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C130" s="31"/>
@@ -6013,7 +6013,7 @@
       <c r="A131" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B131" s="30" t="s">
+      <c r="B131" s="35" t="s">
         <v>37</v>
       </c>
       <c r="C131" s="31"/>
@@ -6025,7 +6025,7 @@
       <c r="A132" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B132" s="30" t="s">
+      <c r="B132" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C132" s="31"/>
@@ -6043,13 +6043,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A26:E26"/>
@@ -6065,6 +6058,13 @@
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
@@ -6087,7 +6087,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="41"/>

--- a/KP_Client_FireProtect.xlsx
+++ b/KP_Client_FireProtect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\fireprotect_kp_bot_mvp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF807168-BF8C-421D-875A-CBDAF306B4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F85033-96F2-4F73-9C96-A5BAF8CE1C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="823">
   <si>
     <t>OFERTĂ COMERCIALĂ</t>
   </si>
@@ -2556,6 +2556,9 @@
   </si>
   <si>
     <t>МП G1/2, l=50 mm Mufă sudată pentru pulverizatoare cu apă fină</t>
+  </si>
+  <si>
+    <t>25 Consolă de sprjin Stex 35/35</t>
   </si>
 </sst>
 </file>
@@ -2822,23 +2825,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2847,6 +2844,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3180,7 +3183,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -3190,7 +3193,7 @@
       <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -3275,7 +3278,7 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="31"/>
@@ -3695,13 +3698,13 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="12">
         <f>SUM(F11:F25)</f>
         <v>135320.625</v>
@@ -3716,7 +3719,7 @@
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B28" s="31"/>
@@ -4136,13 +4139,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
       <c r="F45" s="12">
         <f>SUM(F30:F44)</f>
         <v>0</v>
@@ -4157,7 +4160,7 @@
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="32" t="s">
         <v>20</v>
       </c>
       <c r="B47" s="31"/>
@@ -4577,13 +4580,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
       <c r="F64" s="12">
         <f>SUM(F49:F63)</f>
         <v>56250</v>
@@ -4598,7 +4601,7 @@
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="36" t="s">
+      <c r="A66" s="32" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="31"/>
@@ -5018,13 +5021,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="34"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="34"/>
       <c r="F83" s="12">
         <f>SUM(F68:F82)</f>
         <v>0</v>
@@ -5039,7 +5042,7 @@
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="32" t="s">
         <v>24</v>
       </c>
       <c r="B85" s="31"/>
@@ -5459,13 +5462,13 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="32" t="s">
+      <c r="A102" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="33"/>
-      <c r="C102" s="33"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="33"/>
+      <c r="B102" s="34"/>
+      <c r="C102" s="34"/>
+      <c r="D102" s="34"/>
+      <c r="E102" s="34"/>
       <c r="F102" s="12">
         <f>SUM(F87:F101)</f>
         <v>0</v>
@@ -5480,7 +5483,7 @@
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="36" t="s">
+      <c r="A104" s="32" t="s">
         <v>26</v>
       </c>
       <c r="B104" s="31"/>
@@ -5900,13 +5903,13 @@
       </c>
     </row>
     <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="32" t="s">
+      <c r="A121" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="33"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="33"/>
-      <c r="E121" s="33"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="34"/>
       <c r="F121" s="12">
         <f>SUM(F106:F120)</f>
         <v>0</v>
@@ -5921,7 +5924,7 @@
       <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="39" t="s">
+      <c r="A123" s="37" t="s">
         <v>28</v>
       </c>
       <c r="B123" s="31"/>
@@ -5934,7 +5937,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="39" t="s">
+      <c r="A124" s="37" t="s">
         <v>29</v>
       </c>
       <c r="B124" s="31"/>
@@ -5947,13 +5950,13 @@
       </c>
     </row>
     <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="37" t="s">
+      <c r="A125" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B125" s="38"/>
-      <c r="C125" s="38"/>
-      <c r="D125" s="38"/>
-      <c r="E125" s="38"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="36"/>
+      <c r="D125" s="36"/>
+      <c r="E125" s="36"/>
       <c r="F125" s="14">
         <f>F123+F124</f>
         <v>229884.75</v>
@@ -5976,7 +5979,7 @@
       <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="40" t="s">
+      <c r="A128" s="38" t="s">
         <v>31</v>
       </c>
       <c r="B128" s="31"/>
@@ -5989,7 +5992,7 @@
       <c r="A129" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B129" s="35" t="s">
+      <c r="B129" s="30" t="s">
         <v>33</v>
       </c>
       <c r="C129" s="31"/>
@@ -6001,7 +6004,7 @@
       <c r="A130" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="35" t="s">
+      <c r="B130" s="30" t="s">
         <v>35</v>
       </c>
       <c r="C130" s="31"/>
@@ -6013,7 +6016,7 @@
       <c r="A131" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B131" s="35" t="s">
+      <c r="B131" s="30" t="s">
         <v>37</v>
       </c>
       <c r="C131" s="31"/>
@@ -6025,7 +6028,7 @@
       <c r="A132" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B132" s="35" t="s">
+      <c r="B132" s="30" t="s">
         <v>39</v>
       </c>
       <c r="C132" s="31"/>
@@ -6043,6 +6046,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A26:E26"/>
@@ -6058,13 +6068,6 @@
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
@@ -6087,7 +6090,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="39" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="41"/>
@@ -18777,7 +18780,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
@@ -19470,10 +19473,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>265</v>
+        <v>807</v>
       </c>
       <c r="C64" s="23" t="s">
         <v>340</v>
@@ -19481,10 +19484,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>268</v>
+        <v>808</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C65" s="23" t="s">
         <v>340</v>
@@ -19492,10 +19495,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C66" s="23" t="s">
         <v>340</v>
@@ -19503,10 +19506,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>264</v>
+        <v>809</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="C67" s="23" t="s">
         <v>340</v>
@@ -19514,9 +19517,20 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>264</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
         <v>815</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>816</v>
       </c>
     </row>

--- a/KP_Client_FireProtect.xlsx
+++ b/KP_Client_FireProtect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\fireprotect_kp_bot_mvp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F85033-96F2-4F73-9C96-A5BAF8CE1C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F99611C-472C-468E-A064-A80174A26649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="824">
   <si>
     <t>OFERTĂ COMERCIALĂ</t>
   </si>
@@ -2559,6 +2559,9 @@
   </si>
   <si>
     <t>25 Consolă de sprjin Stex 35/35</t>
+  </si>
+  <si>
+    <t>Consolă de sprijin Stex 35/35</t>
   </si>
 </sst>
 </file>
@@ -2825,17 +2828,23 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2844,12 +2853,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3183,7 +3186,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -3193,7 +3196,7 @@
       <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -3278,7 +3281,7 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="36" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="31"/>
@@ -3698,13 +3701,13 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="12">
         <f>SUM(F11:F25)</f>
         <v>135320.625</v>
@@ -3719,7 +3722,7 @@
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B28" s="31"/>
@@ -4139,13 +4142,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
       <c r="F45" s="12">
         <f>SUM(F30:F44)</f>
         <v>0</v>
@@ -4160,7 +4163,7 @@
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B47" s="31"/>
@@ -4580,13 +4583,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="33" t="s">
+      <c r="A64" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="34"/>
-      <c r="C64" s="34"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="33"/>
       <c r="F64" s="12">
         <f>SUM(F49:F63)</f>
         <v>56250</v>
@@ -4601,7 +4604,7 @@
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="36" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="31"/>
@@ -5021,13 +5024,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="33" t="s">
+      <c r="A83" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B83" s="34"/>
-      <c r="C83" s="34"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="34"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="33"/>
       <c r="F83" s="12">
         <f>SUM(F68:F82)</f>
         <v>0</v>
@@ -5042,7 +5045,7 @@
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B85" s="31"/>
@@ -5462,13 +5465,13 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="33" t="s">
+      <c r="A102" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="34"/>
-      <c r="C102" s="34"/>
-      <c r="D102" s="34"/>
-      <c r="E102" s="34"/>
+      <c r="B102" s="33"/>
+      <c r="C102" s="33"/>
+      <c r="D102" s="33"/>
+      <c r="E102" s="33"/>
       <c r="F102" s="12">
         <f>SUM(F87:F101)</f>
         <v>0</v>
@@ -5483,7 +5486,7 @@
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="32" t="s">
+      <c r="A104" s="36" t="s">
         <v>26</v>
       </c>
       <c r="B104" s="31"/>
@@ -5903,13 +5906,13 @@
       </c>
     </row>
     <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="33" t="s">
+      <c r="A121" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="34"/>
-      <c r="C121" s="34"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="34"/>
+      <c r="B121" s="33"/>
+      <c r="C121" s="33"/>
+      <c r="D121" s="33"/>
+      <c r="E121" s="33"/>
       <c r="F121" s="12">
         <f>SUM(F106:F120)</f>
         <v>0</v>
@@ -5924,7 +5927,7 @@
       <c r="F122" s="1"/>
     </row>
     <row r="123" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="37" t="s">
+      <c r="A123" s="39" t="s">
         <v>28</v>
       </c>
       <c r="B123" s="31"/>
@@ -5937,7 +5940,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="37" t="s">
+      <c r="A124" s="39" t="s">
         <v>29</v>
       </c>
       <c r="B124" s="31"/>
@@ -5950,13 +5953,13 @@
       </c>
     </row>
     <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="35" t="s">
+      <c r="A125" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B125" s="36"/>
-      <c r="C125" s="36"/>
-      <c r="D125" s="36"/>
-      <c r="E125" s="36"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="38"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="38"/>
       <c r="F125" s="14">
         <f>F123+F124</f>
         <v>229884.75</v>
@@ -5979,7 +5982,7 @@
       <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="38" t="s">
+      <c r="A128" s="40" t="s">
         <v>31</v>
       </c>
       <c r="B128" s="31"/>
@@ -5992,7 +5995,7 @@
       <c r="A129" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B129" s="30" t="s">
+      <c r="B129" s="35" t="s">
         <v>33</v>
       </c>
       <c r="C129" s="31"/>
@@ -6004,7 +6007,7 @@
       <c r="A130" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="30" t="s">
+      <c r="B130" s="35" t="s">
         <v>35</v>
       </c>
       <c r="C130" s="31"/>
@@ -6016,7 +6019,7 @@
       <c r="A131" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B131" s="30" t="s">
+      <c r="B131" s="35" t="s">
         <v>37</v>
       </c>
       <c r="C131" s="31"/>
@@ -6028,7 +6031,7 @@
       <c r="A132" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B132" s="30" t="s">
+      <c r="B132" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C132" s="31"/>
@@ -6046,13 +6049,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A26:E26"/>
@@ -6068,6 +6064,13 @@
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
@@ -6090,7 +6093,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="41"/>
@@ -18780,7 +18783,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64" customWidth="1"/>
@@ -19484,10 +19487,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>265</v>
+        <v>807</v>
       </c>
       <c r="C65" s="23" t="s">
         <v>340</v>
@@ -19495,10 +19498,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>268</v>
+        <v>808</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C66" s="23" t="s">
         <v>340</v>
@@ -19506,10 +19509,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C67" s="23" t="s">
         <v>340</v>
@@ -19517,10 +19520,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>264</v>
+        <v>809</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="C68" s="23" t="s">
         <v>340</v>
@@ -19528,9 +19531,20 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>264</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
         <v>815</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>816</v>
       </c>
     </row>

--- a/KP_Client_FireProtect.xlsx
+++ b/KP_Client_FireProtect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\fireprotect_kp_bot_mvp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F99611C-472C-468E-A064-A80174A26649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECA2DDE-E880-40EF-B339-3D654B818401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KP_Client" sheetId="1" r:id="rId1"/>
@@ -2828,23 +2828,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2853,6 +2847,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3175,7 +3175,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3186,7 +3186,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -3196,7 +3196,7 @@
       <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -3281,7 +3281,7 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="31"/>
@@ -3311,2766 +3311,3168 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="9">
-        <f>IF(Introducere_interna!$B6="","",1)</f>
-        <v>1</v>
-      </c>
-      <c r="B11" s="10" t="str">
-        <f>IF(Introducere_interna!$B6="","",Introducere_interna!$C6)</f>
-        <v>Sprinkler incendiu CBSO-PVo 0.08 R1/2 P57.B3</v>
-      </c>
-      <c r="C11" s="9" t="str">
-        <f>IF(Introducere_interna!$B6="","",Introducere_interna!$D6)</f>
-        <v>buc</v>
-      </c>
-      <c r="D11" s="9">
-        <f>IF(Introducere_interna!$B6="","",Introducere_interna!$E6)</f>
-        <v>850</v>
-      </c>
-      <c r="E11" s="11">
-        <f>IF(Introducere_interna!$B6="","",Introducere_interna!$F6)</f>
-        <v>156.11250000000001</v>
-      </c>
-      <c r="F11" s="11">
-        <f>IF(Introducere_interna!$B6="","",Introducere_interna!$G6)</f>
-        <v>132695.625</v>
-      </c>
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="9">
-        <f>IF(Introducere_interna!$B7="","",2)</f>
-        <v>2</v>
-      </c>
-      <c r="B12" s="10" t="str">
-        <f>IF(Introducere_interna!$B7="","",Introducere_interna!$C7)</f>
-        <v/>
-      </c>
-      <c r="C12" s="9" t="str">
-        <f>IF(Introducere_interna!$B7="","",Introducere_interna!$D7)</f>
-        <v/>
-      </c>
-      <c r="D12" s="9">
-        <f>IF(Introducere_interna!$B7="","",Introducere_interna!$E7)</f>
-        <v>120</v>
-      </c>
-      <c r="E12" s="11" t="str">
-        <f>IF(Introducere_interna!$B7="","",Introducere_interna!$F7)</f>
-        <v/>
-      </c>
-      <c r="F12" s="11" t="str">
-        <f>IF(Introducere_interna!$B7="","",Introducere_interna!$G7)</f>
-        <v/>
-      </c>
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="9">
-        <f>IF(Introducere_interna!$B8="","",3)</f>
-        <v>3</v>
-      </c>
-      <c r="B13" s="10" t="str">
-        <f>IF(Introducere_interna!$B8="","",Introducere_interna!$C8)</f>
-        <v>Țeavă zincată DN15*2.2mm</v>
-      </c>
-      <c r="C13" s="9" t="str">
-        <f>IF(Introducere_interna!$B8="","",Introducere_interna!$D8)</f>
-        <v>m</v>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(Introducere_interna!$B8="","",Introducere_interna!$E8)</f>
-        <v>500</v>
-      </c>
-      <c r="E13" s="11" t="str">
-        <f>IF(Introducere_interna!$B8="","",Introducere_interna!$F8)</f>
-        <v/>
-      </c>
-      <c r="F13" s="11" t="str">
-        <f>IF(Introducere_interna!$B8="","",Introducere_interna!$G8)</f>
-        <v/>
-      </c>
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="9">
-        <f>IF(Introducere_interna!$B9="","",4)</f>
-        <v>4</v>
-      </c>
-      <c r="B14" s="10" t="str">
-        <f>IF(Introducere_interna!$B9="","",Introducere_interna!$C9)</f>
-        <v>Țeavă zincată DN15*2.8mm</v>
-      </c>
-      <c r="C14" s="9" t="str">
-        <f>IF(Introducere_interna!$B9="","",Introducere_interna!$D9)</f>
-        <v>m</v>
-      </c>
-      <c r="D14" s="9">
-        <f>IF(Introducere_interna!$B9="","",Introducere_interna!$E9)</f>
-        <v>20</v>
-      </c>
-      <c r="E14" s="11" t="str">
-        <f>IF(Introducere_interna!$B9="","",Introducere_interna!$F9)</f>
-        <v/>
-      </c>
-      <c r="F14" s="11" t="str">
-        <f>IF(Introducere_interna!$B9="","",Introducere_interna!$G9)</f>
-        <v/>
-      </c>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="9">
-        <f>IF(Introducere_interna!$B10="","",5)</f>
-        <v>5</v>
-      </c>
-      <c r="B15" s="10" t="str">
-        <f>IF(Introducere_interna!$B10="","",Introducere_interna!$C10)</f>
-        <v>Țeavă zincată DN32*2.8mm</v>
-      </c>
-      <c r="C15" s="9" t="str">
-        <f>IF(Introducere_interna!$B10="","",Introducere_interna!$D10)</f>
-        <v>m</v>
-      </c>
-      <c r="D15" s="9">
-        <f>IF(Introducere_interna!$B10="","",Introducere_interna!$E10)</f>
-        <v>50</v>
-      </c>
-      <c r="E15" s="11">
-        <f>IF(Introducere_interna!$B10="","",Introducere_interna!$F10)</f>
-        <v>52.5</v>
-      </c>
-      <c r="F15" s="11">
-        <f>IF(Introducere_interna!$B10="","",Introducere_interna!$G10)</f>
-        <v>2625</v>
-      </c>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="9">
-        <f>IF(Introducere_interna!$B11="","",6)</f>
-        <v>6</v>
-      </c>
-      <c r="B16" s="10" t="str">
-        <f>IF(Introducere_interna!$B11="","",Introducere_interna!$C11)</f>
-        <v/>
-      </c>
-      <c r="C16" s="9" t="str">
-        <f>IF(Introducere_interna!$B11="","",Introducere_interna!$D11)</f>
-        <v/>
-      </c>
-      <c r="D16" s="9">
-        <f>IF(Introducere_interna!$B11="","",Introducere_interna!$E11)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="11" t="str">
-        <f>IF(Introducere_interna!$B11="","",Introducere_interna!$F11)</f>
-        <v/>
-      </c>
-      <c r="F16" s="11" t="str">
-        <f>IF(Introducere_interna!$B11="","",Introducere_interna!$G11)</f>
-        <v/>
-      </c>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="9">
-        <f>IF(Introducere_interna!$B12="","",7)</f>
-        <v>7</v>
-      </c>
-      <c r="B17" s="10" t="str">
-        <f>IF(Introducere_interna!$B12="","",Introducere_interna!$C12)</f>
-        <v>Țeavă zincată DN15*2.2mm</v>
-      </c>
-      <c r="C17" s="9" t="str">
-        <f>IF(Introducere_interna!$B12="","",Introducere_interna!$D12)</f>
-        <v>m</v>
-      </c>
-      <c r="D17" s="9">
-        <f>IF(Introducere_interna!$B12="","",Introducere_interna!$E12)</f>
-        <v>225</v>
-      </c>
-      <c r="E17" s="11" t="str">
-        <f>IF(Introducere_interna!$B12="","",Introducere_interna!$F12)</f>
-        <v/>
-      </c>
-      <c r="F17" s="11" t="str">
-        <f>IF(Introducere_interna!$B12="","",Introducere_interna!$G12)</f>
-        <v/>
-      </c>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="9" t="str">
-        <f>IF(Introducere_interna!$B13="","",8)</f>
-        <v/>
-      </c>
-      <c r="B18" s="10" t="str">
-        <f>IF(Introducere_interna!$B13="","",Introducere_interna!$C13)</f>
-        <v/>
-      </c>
-      <c r="C18" s="9" t="str">
-        <f>IF(Introducere_interna!$B13="","",Introducere_interna!$D13)</f>
-        <v/>
-      </c>
-      <c r="D18" s="9" t="str">
-        <f>IF(Introducere_interna!$B13="","",Introducere_interna!$E13)</f>
-        <v/>
-      </c>
-      <c r="E18" s="11" t="str">
-        <f>IF(Introducere_interna!$B13="","",Introducere_interna!$F13)</f>
-        <v/>
-      </c>
-      <c r="F18" s="11" t="str">
-        <f>IF(Introducere_interna!$B13="","",Introducere_interna!$G13)</f>
-        <v/>
-      </c>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="9" t="str">
-        <f>IF(Introducere_interna!$B14="","",9)</f>
-        <v/>
-      </c>
-      <c r="B19" s="10" t="str">
-        <f>IF(Introducere_interna!$B14="","",Introducere_interna!$C14)</f>
-        <v/>
-      </c>
-      <c r="C19" s="9" t="str">
-        <f>IF(Introducere_interna!$B14="","",Introducere_interna!$D14)</f>
-        <v/>
-      </c>
-      <c r="D19" s="9" t="str">
-        <f>IF(Introducere_interna!$B14="","",Introducere_interna!$E14)</f>
-        <v/>
-      </c>
-      <c r="E19" s="11" t="str">
-        <f>IF(Introducere_interna!$B14="","",Introducere_interna!$F14)</f>
-        <v/>
-      </c>
-      <c r="F19" s="11" t="str">
-        <f>IF(Introducere_interna!$B14="","",Introducere_interna!$G14)</f>
-        <v/>
-      </c>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="9" t="str">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+    </row>
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A45" s="9" t="str">
         <f>IF(Introducere_interna!$B15="","",10)</f>
         <v/>
       </c>
-      <c r="B20" s="10" t="str">
+      <c r="B45" s="10" t="str">
         <f>IF(Introducere_interna!$B15="","",Introducere_interna!$C15)</f>
         <v/>
       </c>
-      <c r="C20" s="9" t="str">
+      <c r="C45" s="9" t="str">
         <f>IF(Introducere_interna!$B15="","",Introducere_interna!$D15)</f>
         <v/>
       </c>
-      <c r="D20" s="9" t="str">
+      <c r="D45" s="9" t="str">
         <f>IF(Introducere_interna!$B15="","",Introducere_interna!$E15)</f>
         <v/>
       </c>
-      <c r="E20" s="11" t="str">
+      <c r="E45" s="11" t="str">
         <f>IF(Introducere_interna!$B15="","",Introducere_interna!$F15)</f>
         <v/>
       </c>
-      <c r="F20" s="11" t="str">
+      <c r="F45" s="11" t="str">
         <f>IF(Introducere_interna!$B15="","",Introducere_interna!$G15)</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="9" t="str">
+    <row r="46" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A46" s="9" t="str">
         <f>IF(Introducere_interna!$B16="","",11)</f>
         <v/>
       </c>
-      <c r="B21" s="10" t="str">
+      <c r="B46" s="10" t="str">
         <f>IF(Introducere_interna!$B16="","",Introducere_interna!$C16)</f>
         <v/>
       </c>
-      <c r="C21" s="9" t="str">
+      <c r="C46" s="9" t="str">
         <f>IF(Introducere_interna!$B16="","",Introducere_interna!$D16)</f>
         <v/>
       </c>
-      <c r="D21" s="9" t="str">
+      <c r="D46" s="9" t="str">
         <f>IF(Introducere_interna!$B16="","",Introducere_interna!$E16)</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="str">
+      <c r="E46" s="11" t="str">
         <f>IF(Introducere_interna!$B16="","",Introducere_interna!$F16)</f>
         <v/>
       </c>
-      <c r="F21" s="11" t="str">
+      <c r="F46" s="11" t="str">
         <f>IF(Introducere_interna!$B16="","",Introducere_interna!$G16)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="9" t="str">
+    <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A47" s="9" t="str">
         <f>IF(Introducere_interna!$B17="","",12)</f>
         <v/>
       </c>
-      <c r="B22" s="10" t="str">
+      <c r="B47" s="10" t="str">
         <f>IF(Introducere_interna!$B17="","",Introducere_interna!$C17)</f>
         <v/>
       </c>
-      <c r="C22" s="9" t="str">
+      <c r="C47" s="9" t="str">
         <f>IF(Introducere_interna!$B17="","",Introducere_interna!$D17)</f>
         <v/>
       </c>
-      <c r="D22" s="9" t="str">
+      <c r="D47" s="9" t="str">
         <f>IF(Introducere_interna!$B17="","",Introducere_interna!$E17)</f>
         <v/>
       </c>
-      <c r="E22" s="11" t="str">
+      <c r="E47" s="11" t="str">
         <f>IF(Introducere_interna!$B17="","",Introducere_interna!$F17)</f>
         <v/>
       </c>
-      <c r="F22" s="11" t="str">
+      <c r="F47" s="11" t="str">
         <f>IF(Introducere_interna!$B17="","",Introducere_interna!$G17)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="9" t="str">
+    <row r="48" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A48" s="9" t="str">
         <f>IF(Introducere_interna!$B18="","",13)</f>
         <v/>
       </c>
-      <c r="B23" s="10" t="str">
+      <c r="B48" s="10" t="str">
         <f>IF(Introducere_interna!$B18="","",Introducere_interna!$C18)</f>
         <v/>
       </c>
-      <c r="C23" s="9" t="str">
+      <c r="C48" s="9" t="str">
         <f>IF(Introducere_interna!$B18="","",Introducere_interna!$D18)</f>
         <v/>
       </c>
-      <c r="D23" s="9" t="str">
+      <c r="D48" s="9" t="str">
         <f>IF(Introducere_interna!$B18="","",Introducere_interna!$E18)</f>
         <v/>
       </c>
-      <c r="E23" s="11" t="str">
+      <c r="E48" s="11" t="str">
         <f>IF(Introducere_interna!$B18="","",Introducere_interna!$F18)</f>
         <v/>
       </c>
-      <c r="F23" s="11" t="str">
+      <c r="F48" s="11" t="str">
         <f>IF(Introducere_interna!$B18="","",Introducere_interna!$G18)</f>
         <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="9" t="str">
-        <f>IF(Introducere_interna!$B19="","",14)</f>
-        <v/>
-      </c>
-      <c r="B24" s="10" t="str">
-        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$C19)</f>
-        <v/>
-      </c>
-      <c r="C24" s="9" t="str">
-        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$D19)</f>
-        <v/>
-      </c>
-      <c r="D24" s="9" t="str">
-        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$E19)</f>
-        <v/>
-      </c>
-      <c r="E24" s="11" t="str">
-        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$F19)</f>
-        <v/>
-      </c>
-      <c r="F24" s="11" t="str">
-        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$G19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="9" t="str">
-        <f>IF(Introducere_interna!$B20="","",15)</f>
-        <v/>
-      </c>
-      <c r="B25" s="10" t="str">
-        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$C20)</f>
-        <v/>
-      </c>
-      <c r="C25" s="9" t="str">
-        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$D20)</f>
-        <v/>
-      </c>
-      <c r="D25" s="9" t="str">
-        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$E20)</f>
-        <v/>
-      </c>
-      <c r="E25" s="11" t="str">
-        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$F20)</f>
-        <v/>
-      </c>
-      <c r="F25" s="11" t="str">
-        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$G20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="12">
-        <f>SUM(F11:F25)</f>
-        <v>135320.625</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-    </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="9">
-        <f>IF(Introducere_interna!$B21="","",1)</f>
-        <v>1</v>
-      </c>
-      <c r="B30" s="10" t="str">
-        <f>IF(Introducere_interna!$B21="","",Introducere_interna!$C21)</f>
-        <v>Vană fluture DN50 PN16</v>
-      </c>
-      <c r="C30" s="9" t="str">
-        <f>IF(Introducere_interna!$B21="","",Introducere_interna!$D21)</f>
-        <v>buc</v>
-      </c>
-      <c r="D30" s="9">
-        <f>IF(Introducere_interna!$B21="","",Introducere_interna!$E21)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="11">
-        <f>IF(Introducere_interna!$B21="","",Introducere_interna!$F21)</f>
-        <v>700</v>
-      </c>
-      <c r="F30" s="11" t="str">
-        <f>IF(Introducere_interna!$B21="","",Introducere_interna!$G21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="9" t="str">
-        <f>IF(Introducere_interna!$B22="","",2)</f>
-        <v/>
-      </c>
-      <c r="B31" s="10" t="str">
-        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$C22)</f>
-        <v/>
-      </c>
-      <c r="C31" s="9" t="str">
-        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$D22)</f>
-        <v/>
-      </c>
-      <c r="D31" s="9" t="str">
-        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$E22)</f>
-        <v/>
-      </c>
-      <c r="E31" s="11" t="str">
-        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$F22)</f>
-        <v/>
-      </c>
-      <c r="F31" s="11" t="str">
-        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$G22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="9" t="str">
-        <f>IF(Introducere_interna!$B23="","",3)</f>
-        <v/>
-      </c>
-      <c r="B32" s="10" t="str">
-        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$C23)</f>
-        <v/>
-      </c>
-      <c r="C32" s="9" t="str">
-        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$D23)</f>
-        <v/>
-      </c>
-      <c r="D32" s="9" t="str">
-        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$E23)</f>
-        <v/>
-      </c>
-      <c r="E32" s="11" t="str">
-        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$F23)</f>
-        <v/>
-      </c>
-      <c r="F32" s="11" t="str">
-        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$G23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="9" t="str">
-        <f>IF(Introducere_interna!$B24="","",4)</f>
-        <v/>
-      </c>
-      <c r="B33" s="10" t="str">
-        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$C24)</f>
-        <v/>
-      </c>
-      <c r="C33" s="9" t="str">
-        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$D24)</f>
-        <v/>
-      </c>
-      <c r="D33" s="9" t="str">
-        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$E24)</f>
-        <v/>
-      </c>
-      <c r="E33" s="11" t="str">
-        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$F24)</f>
-        <v/>
-      </c>
-      <c r="F33" s="11" t="str">
-        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$G24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="9" t="str">
-        <f>IF(Introducere_interna!$B25="","",5)</f>
-        <v/>
-      </c>
-      <c r="B34" s="10" t="str">
-        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$C25)</f>
-        <v/>
-      </c>
-      <c r="C34" s="9" t="str">
-        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$D25)</f>
-        <v/>
-      </c>
-      <c r="D34" s="9" t="str">
-        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$E25)</f>
-        <v/>
-      </c>
-      <c r="E34" s="11" t="str">
-        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$F25)</f>
-        <v/>
-      </c>
-      <c r="F34" s="11" t="str">
-        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$G25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="9" t="str">
-        <f>IF(Introducere_interna!$B26="","",6)</f>
-        <v/>
-      </c>
-      <c r="B35" s="10" t="str">
-        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$C26)</f>
-        <v/>
-      </c>
-      <c r="C35" s="9" t="str">
-        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$D26)</f>
-        <v/>
-      </c>
-      <c r="D35" s="9" t="str">
-        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$E26)</f>
-        <v/>
-      </c>
-      <c r="E35" s="11" t="str">
-        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$F26)</f>
-        <v/>
-      </c>
-      <c r="F35" s="11" t="str">
-        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$G26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="9" t="str">
-        <f>IF(Introducere_interna!$B27="","",7)</f>
-        <v/>
-      </c>
-      <c r="B36" s="10" t="str">
-        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$C27)</f>
-        <v/>
-      </c>
-      <c r="C36" s="9" t="str">
-        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$D27)</f>
-        <v/>
-      </c>
-      <c r="D36" s="9" t="str">
-        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$E27)</f>
-        <v/>
-      </c>
-      <c r="E36" s="11" t="str">
-        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$F27)</f>
-        <v/>
-      </c>
-      <c r="F36" s="11" t="str">
-        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$G27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="9" t="str">
-        <f>IF(Introducere_interna!$B28="","",8)</f>
-        <v/>
-      </c>
-      <c r="B37" s="10" t="str">
-        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$C28)</f>
-        <v/>
-      </c>
-      <c r="C37" s="9" t="str">
-        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$D28)</f>
-        <v/>
-      </c>
-      <c r="D37" s="9" t="str">
-        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$E28)</f>
-        <v/>
-      </c>
-      <c r="E37" s="11" t="str">
-        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$F28)</f>
-        <v/>
-      </c>
-      <c r="F37" s="11" t="str">
-        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$G28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="9" t="str">
-        <f>IF(Introducere_interna!$B29="","",9)</f>
-        <v/>
-      </c>
-      <c r="B38" s="10" t="str">
-        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$C29)</f>
-        <v/>
-      </c>
-      <c r="C38" s="9" t="str">
-        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$D29)</f>
-        <v/>
-      </c>
-      <c r="D38" s="9" t="str">
-        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$E29)</f>
-        <v/>
-      </c>
-      <c r="E38" s="11" t="str">
-        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$F29)</f>
-        <v/>
-      </c>
-      <c r="F38" s="11" t="str">
-        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$G29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="9" t="str">
-        <f>IF(Introducere_interna!$B30="","",10)</f>
-        <v/>
-      </c>
-      <c r="B39" s="10" t="str">
-        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$C30)</f>
-        <v/>
-      </c>
-      <c r="C39" s="9" t="str">
-        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$D30)</f>
-        <v/>
-      </c>
-      <c r="D39" s="9" t="str">
-        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$E30)</f>
-        <v/>
-      </c>
-      <c r="E39" s="11" t="str">
-        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$F30)</f>
-        <v/>
-      </c>
-      <c r="F39" s="11" t="str">
-        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$G30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="9" t="str">
-        <f>IF(Introducere_interna!$B31="","",11)</f>
-        <v/>
-      </c>
-      <c r="B40" s="10" t="str">
-        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$C31)</f>
-        <v/>
-      </c>
-      <c r="C40" s="9" t="str">
-        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$D31)</f>
-        <v/>
-      </c>
-      <c r="D40" s="9" t="str">
-        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$E31)</f>
-        <v/>
-      </c>
-      <c r="E40" s="11" t="str">
-        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$F31)</f>
-        <v/>
-      </c>
-      <c r="F40" s="11" t="str">
-        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$G31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="9" t="str">
-        <f>IF(Introducere_interna!$B32="","",12)</f>
-        <v/>
-      </c>
-      <c r="B41" s="10" t="str">
-        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$C32)</f>
-        <v/>
-      </c>
-      <c r="C41" s="9" t="str">
-        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$D32)</f>
-        <v/>
-      </c>
-      <c r="D41" s="9" t="str">
-        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$E32)</f>
-        <v/>
-      </c>
-      <c r="E41" s="11" t="str">
-        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$F32)</f>
-        <v/>
-      </c>
-      <c r="F41" s="11" t="str">
-        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$G32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="9" t="str">
-        <f>IF(Introducere_interna!$B33="","",13)</f>
-        <v/>
-      </c>
-      <c r="B42" s="10" t="str">
-        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$C33)</f>
-        <v/>
-      </c>
-      <c r="C42" s="9" t="str">
-        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$D33)</f>
-        <v/>
-      </c>
-      <c r="D42" s="9" t="str">
-        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$E33)</f>
-        <v/>
-      </c>
-      <c r="E42" s="11" t="str">
-        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$F33)</f>
-        <v/>
-      </c>
-      <c r="F42" s="11" t="str">
-        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$G33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="9" t="str">
-        <f>IF(Introducere_interna!$B34="","",14)</f>
-        <v/>
-      </c>
-      <c r="B43" s="10" t="str">
-        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$C34)</f>
-        <v/>
-      </c>
-      <c r="C43" s="9" t="str">
-        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$D34)</f>
-        <v/>
-      </c>
-      <c r="D43" s="9" t="str">
-        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$E34)</f>
-        <v/>
-      </c>
-      <c r="E43" s="11" t="str">
-        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$F34)</f>
-        <v/>
-      </c>
-      <c r="F43" s="11" t="str">
-        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$G34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="9" t="str">
-        <f>IF(Introducere_interna!$B35="","",15)</f>
-        <v/>
-      </c>
-      <c r="B44" s="10" t="str">
-        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$C35)</f>
-        <v/>
-      </c>
-      <c r="C44" s="9" t="str">
-        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$D35)</f>
-        <v/>
-      </c>
-      <c r="D44" s="9" t="str">
-        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$E35)</f>
-        <v/>
-      </c>
-      <c r="E44" s="11" t="str">
-        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$F35)</f>
-        <v/>
-      </c>
-      <c r="F44" s="11" t="str">
-        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$G35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="12">
-        <f>SUM(F30:F44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-    </row>
-    <row r="48" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A49" s="9" t="str">
-        <f>IF(Introducere_interna!$B36="","",1)</f>
+        <f>IF(Introducere_interna!$B19="","",14)</f>
         <v/>
       </c>
       <c r="B49" s="10" t="str">
-        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$C36)</f>
+        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$C19)</f>
         <v/>
       </c>
       <c r="C49" s="9" t="str">
-        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$D36)</f>
+        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$D19)</f>
         <v/>
       </c>
       <c r="D49" s="9" t="str">
-        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$E36)</f>
+        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$E19)</f>
         <v/>
       </c>
       <c r="E49" s="11" t="str">
-        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$F36)</f>
+        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$F19)</f>
         <v/>
       </c>
       <c r="F49" s="11" t="str">
-        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$G36)</f>
+        <f>IF(Introducere_interna!$B19="","",Introducere_interna!$G19)</f>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A50" s="9" t="str">
-        <f>IF(Introducere_interna!$B37="","",2)</f>
+        <f>IF(Introducere_interna!$B20="","",15)</f>
         <v/>
       </c>
       <c r="B50" s="10" t="str">
-        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$C37)</f>
+        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$C20)</f>
         <v/>
       </c>
       <c r="C50" s="9" t="str">
-        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$D37)</f>
+        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$D20)</f>
         <v/>
       </c>
       <c r="D50" s="9" t="str">
-        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$E37)</f>
+        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$E20)</f>
         <v/>
       </c>
       <c r="E50" s="11" t="str">
-        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$F37)</f>
+        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$F20)</f>
         <v/>
       </c>
       <c r="F50" s="11" t="str">
-        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$G37)</f>
+        <f>IF(Introducere_interna!$B20="","",Introducere_interna!$G20)</f>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="9" t="str">
-        <f>IF(Introducere_interna!$B38="","",3)</f>
-        <v/>
-      </c>
-      <c r="B51" s="10" t="str">
-        <f>IF(Introducere_interna!$B38="","",Introducere_interna!$C38)</f>
-        <v/>
-      </c>
-      <c r="C51" s="9" t="str">
-        <f>IF(Introducere_interna!$B38="","",Introducere_interna!$D38)</f>
-        <v/>
-      </c>
-      <c r="D51" s="9" t="str">
-        <f>IF(Introducere_interna!$B38="","",Introducere_interna!$E38)</f>
-        <v/>
-      </c>
-      <c r="E51" s="11" t="str">
-        <f>IF(Introducere_interna!$B38="","",Introducere_interna!$F38)</f>
-        <v/>
-      </c>
-      <c r="F51" s="11" t="str">
-        <f>IF(Introducere_interna!$B38="","",Introducere_interna!$G38)</f>
-        <v/>
+      <c r="A51" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="12">
+        <f>SUM(F20:F50)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="9">
-        <f>IF(Introducere_interna!$B39="","",4)</f>
-        <v>4</v>
-      </c>
-      <c r="B52" s="10" t="str">
-        <f>IF(Introducere_interna!$B39="","",Introducere_interna!$C39)</f>
-        <v>Rezervor apă</v>
-      </c>
-      <c r="C52" s="9" t="str">
-        <f>IF(Introducere_interna!$B39="","",Introducere_interna!$D39)</f>
-        <v>buc</v>
-      </c>
-      <c r="D52" s="9">
-        <f>IF(Introducere_interna!$B39="","",Introducere_interna!$E39)</f>
-        <v>1</v>
-      </c>
-      <c r="E52" s="11">
-        <f>IF(Introducere_interna!$B39="","",Introducere_interna!$F39)</f>
-        <v>56250</v>
-      </c>
-      <c r="F52" s="11">
-        <f>IF(Introducere_interna!$B39="","",Introducere_interna!$G39)</f>
-        <v>56250</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
     </row>
     <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="9" t="str">
-        <f>IF(Introducere_interna!$B40="","",5)</f>
-        <v/>
-      </c>
-      <c r="B53" s="10" t="str">
-        <f>IF(Introducere_interna!$B40="","",Introducere_interna!$C40)</f>
-        <v/>
-      </c>
-      <c r="C53" s="9" t="str">
-        <f>IF(Introducere_interna!$B40="","",Introducere_interna!$D40)</f>
-        <v/>
-      </c>
-      <c r="D53" s="9" t="str">
-        <f>IF(Introducere_interna!$B40="","",Introducere_interna!$E40)</f>
-        <v/>
-      </c>
-      <c r="E53" s="11" t="str">
-        <f>IF(Introducere_interna!$B40="","",Introducere_interna!$F40)</f>
-        <v/>
-      </c>
-      <c r="F53" s="11" t="str">
-        <f>IF(Introducere_interna!$B40="","",Introducere_interna!$G40)</f>
-        <v/>
-      </c>
+      <c r="A53" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
     </row>
     <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="9" t="str">
-        <f>IF(Introducere_interna!$B41="","",6)</f>
-        <v/>
-      </c>
-      <c r="B54" s="10" t="str">
-        <f>IF(Introducere_interna!$B41="","",Introducere_interna!$C41)</f>
-        <v/>
-      </c>
-      <c r="C54" s="9" t="str">
-        <f>IF(Introducere_interna!$B41="","",Introducere_interna!$D41)</f>
-        <v/>
-      </c>
-      <c r="D54" s="9" t="str">
-        <f>IF(Introducere_interna!$B41="","",Introducere_interna!$E41)</f>
-        <v/>
-      </c>
-      <c r="E54" s="11" t="str">
-        <f>IF(Introducere_interna!$B41="","",Introducere_interna!$F41)</f>
-        <v/>
-      </c>
-      <c r="F54" s="11" t="str">
-        <f>IF(Introducere_interna!$B41="","",Introducere_interna!$G41)</f>
-        <v/>
+      <c r="A54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="9" t="str">
-        <f>IF(Introducere_interna!$B42="","",7)</f>
-        <v/>
-      </c>
-      <c r="B55" s="10" t="str">
-        <f>IF(Introducere_interna!$B42="","",Introducere_interna!$C42)</f>
-        <v/>
-      </c>
-      <c r="C55" s="9" t="str">
-        <f>IF(Introducere_interna!$B42="","",Introducere_interna!$D42)</f>
-        <v/>
-      </c>
-      <c r="D55" s="9" t="str">
-        <f>IF(Introducere_interna!$B42="","",Introducere_interna!$E42)</f>
-        <v/>
-      </c>
-      <c r="E55" s="11" t="str">
-        <f>IF(Introducere_interna!$B42="","",Introducere_interna!$F42)</f>
-        <v/>
-      </c>
-      <c r="F55" s="11" t="str">
-        <f>IF(Introducere_interna!$B42="","",Introducere_interna!$G42)</f>
-        <v/>
-      </c>
+      <c r="A55" s="9"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
     </row>
     <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="9" t="str">
-        <f>IF(Introducere_interna!$B43="","",8)</f>
-        <v/>
-      </c>
-      <c r="B56" s="10" t="str">
-        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$C43)</f>
-        <v/>
-      </c>
-      <c r="C56" s="9" t="str">
-        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$D43)</f>
-        <v/>
-      </c>
-      <c r="D56" s="9" t="str">
-        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$E43)</f>
-        <v/>
-      </c>
-      <c r="E56" s="11" t="str">
-        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$F43)</f>
-        <v/>
-      </c>
-      <c r="F56" s="11" t="str">
-        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$G43)</f>
-        <v/>
-      </c>
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
     </row>
     <row r="57" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="9" t="str">
-        <f>IF(Introducere_interna!$B44="","",9)</f>
-        <v/>
-      </c>
-      <c r="B57" s="10" t="str">
-        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$C44)</f>
-        <v/>
-      </c>
-      <c r="C57" s="9" t="str">
-        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$D44)</f>
-        <v/>
-      </c>
-      <c r="D57" s="9" t="str">
-        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$E44)</f>
-        <v/>
-      </c>
-      <c r="E57" s="11" t="str">
-        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$F44)</f>
-        <v/>
-      </c>
-      <c r="F57" s="11" t="str">
-        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$G44)</f>
-        <v/>
-      </c>
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
     </row>
     <row r="58" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="9" t="str">
-        <f>IF(Introducere_interna!$B45="","",10)</f>
-        <v/>
-      </c>
-      <c r="B58" s="10" t="str">
-        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$C45)</f>
-        <v/>
-      </c>
-      <c r="C58" s="9" t="str">
-        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$D45)</f>
-        <v/>
-      </c>
-      <c r="D58" s="9" t="str">
-        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$E45)</f>
-        <v/>
-      </c>
-      <c r="E58" s="11" t="str">
-        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$F45)</f>
-        <v/>
-      </c>
-      <c r="F58" s="11" t="str">
-        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$G45)</f>
-        <v/>
-      </c>
+      <c r="A58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
     </row>
     <row r="59" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="9" t="str">
-        <f>IF(Introducere_interna!$B46="","",11)</f>
-        <v/>
-      </c>
-      <c r="B59" s="10" t="str">
-        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$C46)</f>
-        <v/>
-      </c>
-      <c r="C59" s="9" t="str">
-        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$D46)</f>
-        <v/>
-      </c>
-      <c r="D59" s="9" t="str">
-        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$E46)</f>
-        <v/>
-      </c>
-      <c r="E59" s="11" t="str">
-        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$F46)</f>
-        <v/>
-      </c>
-      <c r="F59" s="11" t="str">
-        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$G46)</f>
-        <v/>
-      </c>
+      <c r="A59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="9" t="str">
-        <f>IF(Introducere_interna!$B47="","",12)</f>
-        <v/>
-      </c>
-      <c r="B60" s="10" t="str">
-        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$C47)</f>
-        <v/>
-      </c>
-      <c r="C60" s="9" t="str">
-        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$D47)</f>
-        <v/>
-      </c>
-      <c r="D60" s="9" t="str">
-        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$E47)</f>
-        <v/>
-      </c>
-      <c r="E60" s="11" t="str">
-        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$F47)</f>
-        <v/>
-      </c>
-      <c r="F60" s="11" t="str">
-        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$G47)</f>
-        <v/>
-      </c>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="9" t="str">
-        <f>IF(Introducere_interna!$B48="","",13)</f>
-        <v/>
-      </c>
-      <c r="B61" s="10" t="str">
-        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$C48)</f>
-        <v/>
-      </c>
-      <c r="C61" s="9" t="str">
-        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$D48)</f>
-        <v/>
-      </c>
-      <c r="D61" s="9" t="str">
-        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$E48)</f>
-        <v/>
-      </c>
-      <c r="E61" s="11" t="str">
-        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$F48)</f>
-        <v/>
-      </c>
-      <c r="F61" s="11" t="str">
-        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$G48)</f>
-        <v/>
-      </c>
+      <c r="A61" s="9"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="9" t="str">
-        <f>IF(Introducere_interna!$B49="","",14)</f>
-        <v/>
-      </c>
-      <c r="B62" s="10" t="str">
-        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$C49)</f>
-        <v/>
-      </c>
-      <c r="C62" s="9" t="str">
-        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$D49)</f>
-        <v/>
-      </c>
-      <c r="D62" s="9" t="str">
-        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$E49)</f>
-        <v/>
-      </c>
-      <c r="E62" s="11" t="str">
-        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$F49)</f>
-        <v/>
-      </c>
-      <c r="F62" s="11" t="str">
-        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$G49)</f>
-        <v/>
-      </c>
+      <c r="A62" s="9"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="9" t="str">
-        <f>IF(Introducere_interna!$B50="","",15)</f>
-        <v/>
-      </c>
-      <c r="B63" s="10" t="str">
-        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$C50)</f>
-        <v/>
-      </c>
-      <c r="C63" s="9" t="str">
-        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$D50)</f>
-        <v/>
-      </c>
-      <c r="D63" s="9" t="str">
-        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$E50)</f>
-        <v/>
-      </c>
-      <c r="E63" s="11" t="str">
-        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$F50)</f>
-        <v/>
-      </c>
-      <c r="F63" s="11" t="str">
-        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$G50)</f>
-        <v/>
-      </c>
+      <c r="A63" s="9"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
     </row>
     <row r="64" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="12">
-        <f>SUM(F49:F63)</f>
-        <v>56250</v>
-      </c>
+      <c r="A64" s="9"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
     </row>
     <row r="65" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
     </row>
     <row r="66" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
     </row>
     <row r="67" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="A67" s="9"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
     </row>
     <row r="68" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="9" t="str">
-        <f>IF(Introducere_interna!$B51="","",1)</f>
-        <v/>
-      </c>
-      <c r="B68" s="10" t="str">
-        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$C51)</f>
-        <v/>
-      </c>
-      <c r="C68" s="9" t="str">
-        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$D51)</f>
-        <v/>
-      </c>
-      <c r="D68" s="9" t="str">
-        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$E51)</f>
-        <v/>
-      </c>
-      <c r="E68" s="11" t="str">
-        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$F51)</f>
-        <v/>
-      </c>
-      <c r="F68" s="11" t="str">
-        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$G51)</f>
-        <v/>
-      </c>
+      <c r="A68" s="9"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
     </row>
     <row r="69" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="9" t="str">
-        <f>IF(Introducere_interna!$B52="","",2)</f>
-        <v/>
-      </c>
-      <c r="B69" s="10" t="str">
-        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$C52)</f>
-        <v/>
-      </c>
-      <c r="C69" s="9" t="str">
-        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$D52)</f>
-        <v/>
-      </c>
-      <c r="D69" s="9" t="str">
-        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$E52)</f>
-        <v/>
-      </c>
-      <c r="E69" s="11" t="str">
-        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$F52)</f>
-        <v/>
-      </c>
-      <c r="F69" s="11" t="str">
-        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$G52)</f>
-        <v/>
-      </c>
+      <c r="A69" s="9"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
     </row>
     <row r="70" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="9" t="str">
-        <f>IF(Introducere_interna!$B53="","",3)</f>
-        <v/>
-      </c>
-      <c r="B70" s="10" t="str">
-        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$C53)</f>
-        <v/>
-      </c>
-      <c r="C70" s="9" t="str">
-        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$D53)</f>
-        <v/>
-      </c>
-      <c r="D70" s="9" t="str">
-        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$E53)</f>
-        <v/>
-      </c>
-      <c r="E70" s="11" t="str">
-        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$F53)</f>
-        <v/>
-      </c>
-      <c r="F70" s="11" t="str">
-        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$G53)</f>
-        <v/>
-      </c>
+      <c r="A70" s="9"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
     </row>
     <row r="71" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="9" t="str">
-        <f>IF(Introducere_interna!$B54="","",4)</f>
-        <v/>
-      </c>
-      <c r="B71" s="10" t="str">
-        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$C54)</f>
-        <v/>
-      </c>
-      <c r="C71" s="9" t="str">
-        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$D54)</f>
-        <v/>
-      </c>
-      <c r="D71" s="9" t="str">
-        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$E54)</f>
-        <v/>
-      </c>
-      <c r="E71" s="11" t="str">
-        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$F54)</f>
-        <v/>
-      </c>
-      <c r="F71" s="11" t="str">
-        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$G54)</f>
-        <v/>
-      </c>
+      <c r="A71" s="9"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
     </row>
     <row r="72" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="9" t="str">
-        <f>IF(Introducere_interna!$B55="","",5)</f>
-        <v/>
-      </c>
-      <c r="B72" s="10" t="str">
-        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$C55)</f>
-        <v/>
-      </c>
-      <c r="C72" s="9" t="str">
-        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$D55)</f>
-        <v/>
-      </c>
-      <c r="D72" s="9" t="str">
-        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$E55)</f>
-        <v/>
-      </c>
-      <c r="E72" s="11" t="str">
-        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$F55)</f>
-        <v/>
-      </c>
-      <c r="F72" s="11" t="str">
-        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$G55)</f>
-        <v/>
-      </c>
+      <c r="A72" s="9"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
     </row>
     <row r="73" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="9" t="str">
-        <f>IF(Introducere_interna!$B56="","",6)</f>
-        <v/>
-      </c>
-      <c r="B73" s="10" t="str">
-        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$C56)</f>
-        <v/>
-      </c>
-      <c r="C73" s="9" t="str">
-        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$D56)</f>
-        <v/>
-      </c>
-      <c r="D73" s="9" t="str">
-        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$E56)</f>
-        <v/>
-      </c>
-      <c r="E73" s="11" t="str">
-        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$F56)</f>
-        <v/>
-      </c>
-      <c r="F73" s="11" t="str">
-        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$G56)</f>
-        <v/>
-      </c>
+      <c r="A73" s="9"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
     </row>
     <row r="74" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="9" t="str">
-        <f>IF(Introducere_interna!$B57="","",7)</f>
+        <f>IF(Introducere_interna!$B22="","",2)</f>
         <v/>
       </c>
       <c r="B74" s="10" t="str">
-        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$C57)</f>
+        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$C22)</f>
         <v/>
       </c>
       <c r="C74" s="9" t="str">
-        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$D57)</f>
+        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$D22)</f>
         <v/>
       </c>
       <c r="D74" s="9" t="str">
-        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$E57)</f>
+        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$E22)</f>
         <v/>
       </c>
       <c r="E74" s="11" t="str">
-        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$F57)</f>
+        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$F22)</f>
         <v/>
       </c>
       <c r="F74" s="11" t="str">
-        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$G57)</f>
+        <f>IF(Introducere_interna!$B22="","",Introducere_interna!$G22)</f>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A75" s="9" t="str">
-        <f>IF(Introducere_interna!$B58="","",8)</f>
+        <f>IF(Introducere_interna!$B23="","",3)</f>
         <v/>
       </c>
       <c r="B75" s="10" t="str">
-        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$C58)</f>
+        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$C23)</f>
         <v/>
       </c>
       <c r="C75" s="9" t="str">
-        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$D58)</f>
+        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$D23)</f>
         <v/>
       </c>
       <c r="D75" s="9" t="str">
-        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$E58)</f>
+        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$E23)</f>
         <v/>
       </c>
       <c r="E75" s="11" t="str">
-        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$F58)</f>
+        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$F23)</f>
         <v/>
       </c>
       <c r="F75" s="11" t="str">
-        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$G58)</f>
+        <f>IF(Introducere_interna!$B23="","",Introducere_interna!$G23)</f>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A76" s="9" t="str">
-        <f>IF(Introducere_interna!$B59="","",9)</f>
+        <f>IF(Introducere_interna!$B24="","",4)</f>
         <v/>
       </c>
       <c r="B76" s="10" t="str">
-        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$C59)</f>
+        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$C24)</f>
         <v/>
       </c>
       <c r="C76" s="9" t="str">
-        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$D59)</f>
+        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$D24)</f>
         <v/>
       </c>
       <c r="D76" s="9" t="str">
-        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$E59)</f>
+        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$E24)</f>
         <v/>
       </c>
       <c r="E76" s="11" t="str">
-        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$F59)</f>
+        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$F24)</f>
         <v/>
       </c>
       <c r="F76" s="11" t="str">
-        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$G59)</f>
+        <f>IF(Introducere_interna!$B24="","",Introducere_interna!$G24)</f>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A77" s="9" t="str">
-        <f>IF(Introducere_interna!$B60="","",10)</f>
+        <f>IF(Introducere_interna!$B25="","",5)</f>
         <v/>
       </c>
       <c r="B77" s="10" t="str">
-        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$C60)</f>
+        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$C25)</f>
         <v/>
       </c>
       <c r="C77" s="9" t="str">
-        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$D60)</f>
+        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$D25)</f>
         <v/>
       </c>
       <c r="D77" s="9" t="str">
-        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$E60)</f>
+        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$E25)</f>
         <v/>
       </c>
       <c r="E77" s="11" t="str">
-        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$F60)</f>
+        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$F25)</f>
         <v/>
       </c>
       <c r="F77" s="11" t="str">
-        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$G60)</f>
+        <f>IF(Introducere_interna!$B25="","",Introducere_interna!$G25)</f>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A78" s="9" t="str">
-        <f>IF(Introducere_interna!$B61="","",11)</f>
+        <f>IF(Introducere_interna!$B26="","",6)</f>
         <v/>
       </c>
       <c r="B78" s="10" t="str">
-        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$C61)</f>
+        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$C26)</f>
         <v/>
       </c>
       <c r="C78" s="9" t="str">
-        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$D61)</f>
+        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$D26)</f>
         <v/>
       </c>
       <c r="D78" s="9" t="str">
-        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$E61)</f>
+        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$E26)</f>
         <v/>
       </c>
       <c r="E78" s="11" t="str">
-        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$F61)</f>
+        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$F26)</f>
         <v/>
       </c>
       <c r="F78" s="11" t="str">
-        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$G61)</f>
+        <f>IF(Introducere_interna!$B26="","",Introducere_interna!$G26)</f>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A79" s="9" t="str">
-        <f>IF(Introducere_interna!$B62="","",12)</f>
+        <f>IF(Introducere_interna!$B27="","",7)</f>
         <v/>
       </c>
       <c r="B79" s="10" t="str">
-        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$C62)</f>
+        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$C27)</f>
         <v/>
       </c>
       <c r="C79" s="9" t="str">
-        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$D62)</f>
+        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$D27)</f>
         <v/>
       </c>
       <c r="D79" s="9" t="str">
-        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$E62)</f>
+        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$E27)</f>
         <v/>
       </c>
       <c r="E79" s="11" t="str">
-        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$F62)</f>
+        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$F27)</f>
         <v/>
       </c>
       <c r="F79" s="11" t="str">
-        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$G62)</f>
+        <f>IF(Introducere_interna!$B27="","",Introducere_interna!$G27)</f>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A80" s="9" t="str">
-        <f>IF(Introducere_interna!$B63="","",13)</f>
+        <f>IF(Introducere_interna!$B28="","",8)</f>
         <v/>
       </c>
       <c r="B80" s="10" t="str">
-        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$C63)</f>
+        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$C28)</f>
         <v/>
       </c>
       <c r="C80" s="9" t="str">
-        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$D63)</f>
+        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$D28)</f>
         <v/>
       </c>
       <c r="D80" s="9" t="str">
-        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$E63)</f>
+        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$E28)</f>
         <v/>
       </c>
       <c r="E80" s="11" t="str">
-        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$F63)</f>
+        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$F28)</f>
         <v/>
       </c>
       <c r="F80" s="11" t="str">
-        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$G63)</f>
+        <f>IF(Introducere_interna!$B28="","",Introducere_interna!$G28)</f>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A81" s="9" t="str">
-        <f>IF(Introducere_interna!$B64="","",14)</f>
+        <f>IF(Introducere_interna!$B29="","",9)</f>
         <v/>
       </c>
       <c r="B81" s="10" t="str">
-        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$C64)</f>
+        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$C29)</f>
         <v/>
       </c>
       <c r="C81" s="9" t="str">
-        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$D64)</f>
+        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$D29)</f>
         <v/>
       </c>
       <c r="D81" s="9" t="str">
-        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$E64)</f>
+        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$E29)</f>
         <v/>
       </c>
       <c r="E81" s="11" t="str">
-        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$F64)</f>
+        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$F29)</f>
         <v/>
       </c>
       <c r="F81" s="11" t="str">
-        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$G64)</f>
+        <f>IF(Introducere_interna!$B29="","",Introducere_interna!$G29)</f>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A82" s="9" t="str">
-        <f>IF(Introducere_interna!$B65="","",15)</f>
+        <f>IF(Introducere_interna!$B30="","",10)</f>
         <v/>
       </c>
       <c r="B82" s="10" t="str">
-        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$C65)</f>
+        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$C30)</f>
         <v/>
       </c>
       <c r="C82" s="9" t="str">
-        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$D65)</f>
+        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$D30)</f>
         <v/>
       </c>
       <c r="D82" s="9" t="str">
-        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$E65)</f>
+        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$E30)</f>
         <v/>
       </c>
       <c r="E82" s="11" t="str">
-        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$F65)</f>
+        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$F30)</f>
         <v/>
       </c>
       <c r="F82" s="11" t="str">
-        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$G65)</f>
+        <f>IF(Introducere_interna!$B30="","",Introducere_interna!$G30)</f>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
-      <c r="F83" s="12">
-        <f>SUM(F68:F82)</f>
-        <v>0</v>
+      <c r="A83" s="9" t="str">
+        <f>IF(Introducere_interna!$B31="","",11)</f>
+        <v/>
+      </c>
+      <c r="B83" s="10" t="str">
+        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$C31)</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="str">
+        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$D31)</f>
+        <v/>
+      </c>
+      <c r="D83" s="9" t="str">
+        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$E31)</f>
+        <v/>
+      </c>
+      <c r="E83" s="11" t="str">
+        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$F31)</f>
+        <v/>
+      </c>
+      <c r="F83" s="11" t="str">
+        <f>IF(Introducere_interna!$B31="","",Introducere_interna!$G31)</f>
+        <v/>
       </c>
     </row>
     <row r="84" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
+      <c r="A84" s="9" t="str">
+        <f>IF(Introducere_interna!$B32="","",12)</f>
+        <v/>
+      </c>
+      <c r="B84" s="10" t="str">
+        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$C32)</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="str">
+        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$D32)</f>
+        <v/>
+      </c>
+      <c r="D84" s="9" t="str">
+        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$E32)</f>
+        <v/>
+      </c>
+      <c r="E84" s="11" t="str">
+        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$F32)</f>
+        <v/>
+      </c>
+      <c r="F84" s="11" t="str">
+        <f>IF(Introducere_interna!$B32="","",Introducere_interna!$G32)</f>
+        <v/>
+      </c>
     </row>
     <row r="85" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="31"/>
-      <c r="F85" s="31"/>
+      <c r="A85" s="9" t="str">
+        <f>IF(Introducere_interna!$B33="","",13)</f>
+        <v/>
+      </c>
+      <c r="B85" s="10" t="str">
+        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$C33)</f>
+        <v/>
+      </c>
+      <c r="C85" s="9" t="str">
+        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$D33)</f>
+        <v/>
+      </c>
+      <c r="D85" s="9" t="str">
+        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$E33)</f>
+        <v/>
+      </c>
+      <c r="E85" s="11" t="str">
+        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$F33)</f>
+        <v/>
+      </c>
+      <c r="F85" s="11" t="str">
+        <f>IF(Introducere_interna!$B33="","",Introducere_interna!$G33)</f>
+        <v/>
+      </c>
     </row>
     <row r="86" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>16</v>
+      <c r="A86" s="9" t="str">
+        <f>IF(Introducere_interna!$B34="","",14)</f>
+        <v/>
+      </c>
+      <c r="B86" s="10" t="str">
+        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$C34)</f>
+        <v/>
+      </c>
+      <c r="C86" s="9" t="str">
+        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$D34)</f>
+        <v/>
+      </c>
+      <c r="D86" s="9" t="str">
+        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$E34)</f>
+        <v/>
+      </c>
+      <c r="E86" s="11" t="str">
+        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$F34)</f>
+        <v/>
+      </c>
+      <c r="F86" s="11" t="str">
+        <f>IF(Introducere_interna!$B34="","",Introducere_interna!$G34)</f>
+        <v/>
       </c>
     </row>
     <row r="87" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A87" s="9" t="str">
-        <f>IF(Introducere_interna!$B66="","",1)</f>
+        <f>IF(Introducere_interna!$B35="","",15)</f>
         <v/>
       </c>
       <c r="B87" s="10" t="str">
-        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$C66)</f>
+        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$C35)</f>
         <v/>
       </c>
       <c r="C87" s="9" t="str">
-        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$D66)</f>
+        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$D35)</f>
         <v/>
       </c>
       <c r="D87" s="9" t="str">
-        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$E66)</f>
+        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$E35)</f>
         <v/>
       </c>
       <c r="E87" s="11" t="str">
-        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$F66)</f>
+        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$F35)</f>
         <v/>
       </c>
       <c r="F87" s="11" t="str">
-        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$G66)</f>
+        <f>IF(Introducere_interna!$B35="","",Introducere_interna!$G35)</f>
         <v/>
       </c>
     </row>
     <row r="88" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="9" t="str">
-        <f>IF(Introducere_interna!$B67="","",2)</f>
-        <v/>
-      </c>
-      <c r="B88" s="10" t="str">
-        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$C67)</f>
-        <v/>
-      </c>
-      <c r="C88" s="9" t="str">
-        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$D67)</f>
-        <v/>
-      </c>
-      <c r="D88" s="9" t="str">
-        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$E67)</f>
-        <v/>
-      </c>
-      <c r="E88" s="11" t="str">
-        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$F67)</f>
-        <v/>
-      </c>
-      <c r="F88" s="11" t="str">
-        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$G67)</f>
-        <v/>
+      <c r="A88" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="34"/>
+      <c r="C88" s="34"/>
+      <c r="D88" s="34"/>
+      <c r="E88" s="34"/>
+      <c r="F88" s="12">
+        <f>SUM(F73:F87)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="9" t="str">
-        <f>IF(Introducere_interna!$B68="","",3)</f>
-        <v/>
-      </c>
-      <c r="B89" s="10" t="str">
-        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$C68)</f>
-        <v/>
-      </c>
-      <c r="C89" s="9" t="str">
-        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$D68)</f>
-        <v/>
-      </c>
-      <c r="D89" s="9" t="str">
-        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$E68)</f>
-        <v/>
-      </c>
-      <c r="E89" s="11" t="str">
-        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$F68)</f>
-        <v/>
-      </c>
-      <c r="F89" s="11" t="str">
-        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$G68)</f>
-        <v/>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
     </row>
     <row r="90" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="9" t="str">
-        <f>IF(Introducere_interna!$B69="","",4)</f>
-        <v/>
-      </c>
-      <c r="B90" s="10" t="str">
-        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$C69)</f>
-        <v/>
-      </c>
-      <c r="C90" s="9" t="str">
-        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$D69)</f>
-        <v/>
-      </c>
-      <c r="D90" s="9" t="str">
-        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$E69)</f>
-        <v/>
-      </c>
-      <c r="E90" s="11" t="str">
-        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$F69)</f>
-        <v/>
-      </c>
-      <c r="F90" s="11" t="str">
-        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$G69)</f>
-        <v/>
-      </c>
+      <c r="A90" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" s="31"/>
+      <c r="C90" s="31"/>
+      <c r="D90" s="31"/>
+      <c r="E90" s="31"/>
+      <c r="F90" s="31"/>
     </row>
     <row r="91" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="9" t="str">
-        <f>IF(Introducere_interna!$B70="","",5)</f>
-        <v/>
-      </c>
-      <c r="B91" s="10" t="str">
-        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$C70)</f>
-        <v/>
-      </c>
-      <c r="C91" s="9" t="str">
-        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$D70)</f>
-        <v/>
-      </c>
-      <c r="D91" s="9" t="str">
-        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$E70)</f>
-        <v/>
-      </c>
-      <c r="E91" s="11" t="str">
-        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$F70)</f>
-        <v/>
-      </c>
-      <c r="F91" s="11" t="str">
-        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$G70)</f>
-        <v/>
+      <c r="A91" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="9" t="str">
-        <f>IF(Introducere_interna!$B71="","",6)</f>
+        <f>IF(Introducere_interna!$B36="","",1)</f>
         <v/>
       </c>
       <c r="B92" s="10" t="str">
-        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$C71)</f>
+        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$C36)</f>
         <v/>
       </c>
       <c r="C92" s="9" t="str">
-        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$D71)</f>
+        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$D36)</f>
         <v/>
       </c>
       <c r="D92" s="9" t="str">
-        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$E71)</f>
+        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$E36)</f>
         <v/>
       </c>
       <c r="E92" s="11" t="str">
-        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$F71)</f>
+        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$F36)</f>
         <v/>
       </c>
       <c r="F92" s="11" t="str">
-        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$G71)</f>
+        <f>IF(Introducere_interna!$B36="","",Introducere_interna!$G36)</f>
         <v/>
       </c>
     </row>
     <row r="93" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="9" t="str">
-        <f>IF(Introducere_interna!$B72="","",7)</f>
+        <f>IF(Introducere_interna!$B37="","",2)</f>
         <v/>
       </c>
       <c r="B93" s="10" t="str">
-        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$C72)</f>
+        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$C37)</f>
         <v/>
       </c>
       <c r="C93" s="9" t="str">
-        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$D72)</f>
+        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$D37)</f>
         <v/>
       </c>
       <c r="D93" s="9" t="str">
-        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$E72)</f>
+        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$E37)</f>
         <v/>
       </c>
       <c r="E93" s="11" t="str">
-        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$F72)</f>
+        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$F37)</f>
         <v/>
       </c>
       <c r="F93" s="11" t="str">
-        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$G72)</f>
+        <f>IF(Introducere_interna!$B37="","",Introducere_interna!$G37)</f>
         <v/>
       </c>
     </row>
     <row r="94" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="9" t="str">
-        <f>IF(Introducere_interna!$B73="","",8)</f>
-        <v/>
-      </c>
-      <c r="B94" s="10" t="str">
-        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$C73)</f>
-        <v/>
-      </c>
-      <c r="C94" s="9" t="str">
-        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$D73)</f>
-        <v/>
-      </c>
-      <c r="D94" s="9" t="str">
-        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$E73)</f>
-        <v/>
-      </c>
-      <c r="E94" s="11" t="str">
-        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$F73)</f>
-        <v/>
-      </c>
-      <c r="F94" s="11" t="str">
-        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$G73)</f>
-        <v/>
-      </c>
+      <c r="A94" s="9"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
     </row>
     <row r="95" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="9" t="str">
-        <f>IF(Introducere_interna!$B74="","",9)</f>
-        <v/>
-      </c>
-      <c r="B95" s="10" t="str">
-        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$C74)</f>
-        <v/>
-      </c>
-      <c r="C95" s="9" t="str">
-        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$D74)</f>
-        <v/>
-      </c>
-      <c r="D95" s="9" t="str">
-        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$E74)</f>
-        <v/>
-      </c>
-      <c r="E95" s="11" t="str">
-        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$F74)</f>
-        <v/>
-      </c>
-      <c r="F95" s="11" t="str">
-        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$G74)</f>
-        <v/>
-      </c>
+      <c r="A95" s="9"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
     </row>
     <row r="96" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="9" t="str">
-        <f>IF(Introducere_interna!$B75="","",10)</f>
-        <v/>
-      </c>
-      <c r="B96" s="10" t="str">
-        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$C75)</f>
-        <v/>
-      </c>
-      <c r="C96" s="9" t="str">
-        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$D75)</f>
-        <v/>
-      </c>
-      <c r="D96" s="9" t="str">
-        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$E75)</f>
-        <v/>
-      </c>
-      <c r="E96" s="11" t="str">
-        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$F75)</f>
-        <v/>
-      </c>
-      <c r="F96" s="11" t="str">
-        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$G75)</f>
-        <v/>
-      </c>
+      <c r="A96" s="9"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
     </row>
     <row r="97" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="9" t="str">
-        <f>IF(Introducere_interna!$B76="","",11)</f>
-        <v/>
-      </c>
-      <c r="B97" s="10" t="str">
-        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$C76)</f>
-        <v/>
-      </c>
-      <c r="C97" s="9" t="str">
-        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$D76)</f>
-        <v/>
-      </c>
-      <c r="D97" s="9" t="str">
-        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$E76)</f>
-        <v/>
-      </c>
-      <c r="E97" s="11" t="str">
-        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$F76)</f>
-        <v/>
-      </c>
-      <c r="F97" s="11" t="str">
-        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$G76)</f>
-        <v/>
-      </c>
+      <c r="A97" s="9"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
     </row>
     <row r="98" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="9" t="str">
-        <f>IF(Introducere_interna!$B77="","",12)</f>
-        <v/>
-      </c>
-      <c r="B98" s="10" t="str">
-        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$C77)</f>
-        <v/>
-      </c>
-      <c r="C98" s="9" t="str">
-        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$D77)</f>
-        <v/>
-      </c>
-      <c r="D98" s="9" t="str">
-        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$E77)</f>
-        <v/>
-      </c>
-      <c r="E98" s="11" t="str">
-        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$F77)</f>
-        <v/>
-      </c>
-      <c r="F98" s="11" t="str">
-        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$G77)</f>
-        <v/>
-      </c>
+      <c r="A98" s="9"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
     </row>
     <row r="99" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="9" t="str">
-        <f>IF(Introducere_interna!$B78="","",13)</f>
-        <v/>
-      </c>
-      <c r="B99" s="10" t="str">
-        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$C78)</f>
-        <v/>
-      </c>
-      <c r="C99" s="9" t="str">
-        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$D78)</f>
-        <v/>
-      </c>
-      <c r="D99" s="9" t="str">
-        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$E78)</f>
-        <v/>
-      </c>
-      <c r="E99" s="11" t="str">
-        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$F78)</f>
-        <v/>
-      </c>
-      <c r="F99" s="11" t="str">
-        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$G78)</f>
-        <v/>
-      </c>
+      <c r="A99" s="9"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
     </row>
     <row r="100" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="9" t="str">
-        <f>IF(Introducere_interna!$B79="","",14)</f>
-        <v/>
-      </c>
-      <c r="B100" s="10" t="str">
-        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$C79)</f>
-        <v/>
-      </c>
-      <c r="C100" s="9" t="str">
-        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$D79)</f>
-        <v/>
-      </c>
-      <c r="D100" s="9" t="str">
-        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$E79)</f>
-        <v/>
-      </c>
-      <c r="E100" s="11" t="str">
-        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$F79)</f>
-        <v/>
-      </c>
-      <c r="F100" s="11" t="str">
-        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$G79)</f>
-        <v/>
-      </c>
+      <c r="A100" s="9"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
     </row>
     <row r="101" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="9" t="str">
-        <f>IF(Introducere_interna!$B80="","",15)</f>
-        <v/>
-      </c>
-      <c r="B101" s="10" t="str">
-        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$C80)</f>
-        <v/>
-      </c>
-      <c r="C101" s="9" t="str">
-        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$D80)</f>
-        <v/>
-      </c>
-      <c r="D101" s="9" t="str">
-        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$E80)</f>
-        <v/>
-      </c>
-      <c r="E101" s="11" t="str">
-        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$F80)</f>
-        <v/>
-      </c>
-      <c r="F101" s="11" t="str">
-        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$G80)</f>
-        <v/>
-      </c>
+      <c r="A101" s="9"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
     </row>
     <row r="102" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B102" s="33"/>
-      <c r="C102" s="33"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="33"/>
-      <c r="F102" s="12">
-        <f>SUM(F87:F101)</f>
-        <v>0</v>
-      </c>
+      <c r="A102" s="9"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
     </row>
     <row r="103" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
+      <c r="A103" s="9"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
     </row>
     <row r="104" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B104" s="31"/>
-      <c r="C104" s="31"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="31"/>
-      <c r="F104" s="31"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="11"/>
     </row>
     <row r="105" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="A105" s="9"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
     </row>
     <row r="106" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="9" t="str">
-        <f>IF(Introducere_interna!$B81="","",1)</f>
-        <v/>
-      </c>
-      <c r="B106" s="10" t="str">
-        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$C81)</f>
-        <v/>
-      </c>
-      <c r="C106" s="9" t="str">
-        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$D81)</f>
-        <v/>
-      </c>
-      <c r="D106" s="9" t="str">
-        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$E81)</f>
-        <v/>
-      </c>
-      <c r="E106" s="11" t="str">
-        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$F81)</f>
-        <v/>
-      </c>
-      <c r="F106" s="11" t="str">
-        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$G81)</f>
-        <v/>
-      </c>
+      <c r="A106" s="9"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
     </row>
     <row r="107" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="9" t="str">
-        <f>IF(Introducere_interna!$B82="","",2)</f>
-        <v/>
-      </c>
-      <c r="B107" s="10" t="str">
-        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$C82)</f>
-        <v/>
-      </c>
-      <c r="C107" s="9" t="str">
-        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$D82)</f>
-        <v/>
-      </c>
-      <c r="D107" s="9" t="str">
-        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$E82)</f>
-        <v/>
-      </c>
-      <c r="E107" s="11" t="str">
-        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$F82)</f>
-        <v/>
-      </c>
-      <c r="F107" s="11" t="str">
-        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$G82)</f>
-        <v/>
-      </c>
+      <c r="A107" s="9"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
     </row>
     <row r="108" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="9" t="str">
-        <f>IF(Introducere_interna!$B83="","",3)</f>
-        <v/>
-      </c>
-      <c r="B108" s="10" t="str">
-        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$C83)</f>
-        <v/>
-      </c>
-      <c r="C108" s="9" t="str">
-        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$D83)</f>
-        <v/>
-      </c>
-      <c r="D108" s="9" t="str">
-        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$E83)</f>
-        <v/>
-      </c>
-      <c r="E108" s="11" t="str">
-        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$F83)</f>
-        <v/>
-      </c>
-      <c r="F108" s="11" t="str">
-        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$G83)</f>
-        <v/>
-      </c>
+      <c r="A108" s="9"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
     </row>
     <row r="109" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="9" t="str">
-        <f>IF(Introducere_interna!$B84="","",4)</f>
-        <v/>
-      </c>
-      <c r="B109" s="10" t="str">
-        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$C84)</f>
-        <v/>
-      </c>
-      <c r="C109" s="9" t="str">
-        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$D84)</f>
-        <v/>
-      </c>
-      <c r="D109" s="9" t="str">
-        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$E84)</f>
-        <v/>
-      </c>
-      <c r="E109" s="11" t="str">
-        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$F84)</f>
-        <v/>
-      </c>
-      <c r="F109" s="11" t="str">
-        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$G84)</f>
-        <v/>
-      </c>
+      <c r="A109" s="9"/>
+      <c r="B109" s="10"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
     </row>
     <row r="110" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A110" s="9" t="str">
-        <f>IF(Introducere_interna!$B85="","",5)</f>
+        <f>IF(Introducere_interna!$B43="","",8)</f>
         <v/>
       </c>
       <c r="B110" s="10" t="str">
-        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$C85)</f>
+        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$C43)</f>
         <v/>
       </c>
       <c r="C110" s="9" t="str">
-        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$D85)</f>
+        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$D43)</f>
         <v/>
       </c>
       <c r="D110" s="9" t="str">
-        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$E85)</f>
+        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$E43)</f>
         <v/>
       </c>
       <c r="E110" s="11" t="str">
-        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$F85)</f>
+        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$F43)</f>
         <v/>
       </c>
       <c r="F110" s="11" t="str">
-        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$G85)</f>
+        <f>IF(Introducere_interna!$B43="","",Introducere_interna!$G43)</f>
         <v/>
       </c>
     </row>
     <row r="111" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A111" s="9" t="str">
-        <f>IF(Introducere_interna!$B86="","",6)</f>
+        <f>IF(Introducere_interna!$B44="","",9)</f>
         <v/>
       </c>
       <c r="B111" s="10" t="str">
-        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$C86)</f>
+        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$C44)</f>
         <v/>
       </c>
       <c r="C111" s="9" t="str">
-        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$D86)</f>
+        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$D44)</f>
         <v/>
       </c>
       <c r="D111" s="9" t="str">
-        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$E86)</f>
+        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$E44)</f>
         <v/>
       </c>
       <c r="E111" s="11" t="str">
-        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$F86)</f>
+        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$F44)</f>
         <v/>
       </c>
       <c r="F111" s="11" t="str">
-        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$G86)</f>
+        <f>IF(Introducere_interna!$B44="","",Introducere_interna!$G44)</f>
         <v/>
       </c>
     </row>
     <row r="112" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A112" s="9" t="str">
-        <f>IF(Introducere_interna!$B87="","",7)</f>
+        <f>IF(Introducere_interna!$B45="","",10)</f>
         <v/>
       </c>
       <c r="B112" s="10" t="str">
-        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$C87)</f>
+        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$C45)</f>
         <v/>
       </c>
       <c r="C112" s="9" t="str">
-        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$D87)</f>
+        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$D45)</f>
         <v/>
       </c>
       <c r="D112" s="9" t="str">
-        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$E87)</f>
+        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$E45)</f>
         <v/>
       </c>
       <c r="E112" s="11" t="str">
-        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$F87)</f>
+        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$F45)</f>
         <v/>
       </c>
       <c r="F112" s="11" t="str">
-        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$G87)</f>
+        <f>IF(Introducere_interna!$B45="","",Introducere_interna!$G45)</f>
         <v/>
       </c>
     </row>
     <row r="113" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A113" s="9" t="str">
-        <f>IF(Introducere_interna!$B88="","",8)</f>
+        <f>IF(Introducere_interna!$B46="","",11)</f>
         <v/>
       </c>
       <c r="B113" s="10" t="str">
-        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$C88)</f>
+        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$C46)</f>
         <v/>
       </c>
       <c r="C113" s="9" t="str">
-        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$D88)</f>
+        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$D46)</f>
         <v/>
       </c>
       <c r="D113" s="9" t="str">
-        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$E88)</f>
+        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$E46)</f>
         <v/>
       </c>
       <c r="E113" s="11" t="str">
-        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$F88)</f>
+        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$F46)</f>
         <v/>
       </c>
       <c r="F113" s="11" t="str">
-        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$G88)</f>
+        <f>IF(Introducere_interna!$B46="","",Introducere_interna!$G46)</f>
         <v/>
       </c>
     </row>
     <row r="114" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A114" s="9" t="str">
-        <f>IF(Introducere_interna!$B89="","",9)</f>
+        <f>IF(Introducere_interna!$B47="","",12)</f>
         <v/>
       </c>
       <c r="B114" s="10" t="str">
-        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$C89)</f>
+        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$C47)</f>
         <v/>
       </c>
       <c r="C114" s="9" t="str">
-        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$D89)</f>
+        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$D47)</f>
         <v/>
       </c>
       <c r="D114" s="9" t="str">
-        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$E89)</f>
+        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$E47)</f>
         <v/>
       </c>
       <c r="E114" s="11" t="str">
-        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$F89)</f>
+        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$F47)</f>
         <v/>
       </c>
       <c r="F114" s="11" t="str">
-        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$G89)</f>
+        <f>IF(Introducere_interna!$B47="","",Introducere_interna!$G47)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A115" s="9" t="str">
-        <f>IF(Introducere_interna!$B90="","",10)</f>
+        <f>IF(Introducere_interna!$B48="","",13)</f>
         <v/>
       </c>
       <c r="B115" s="10" t="str">
-        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$C90)</f>
+        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$C48)</f>
         <v/>
       </c>
       <c r="C115" s="9" t="str">
-        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$D90)</f>
+        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$D48)</f>
         <v/>
       </c>
       <c r="D115" s="9" t="str">
-        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$E90)</f>
+        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$E48)</f>
         <v/>
       </c>
       <c r="E115" s="11" t="str">
-        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$F90)</f>
+        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$F48)</f>
         <v/>
       </c>
       <c r="F115" s="11" t="str">
-        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$G90)</f>
+        <f>IF(Introducere_interna!$B48="","",Introducere_interna!$G48)</f>
         <v/>
       </c>
     </row>
     <row r="116" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A116" s="9" t="str">
-        <f>IF(Introducere_interna!$B91="","",11)</f>
+        <f>IF(Introducere_interna!$B49="","",14)</f>
         <v/>
       </c>
       <c r="B116" s="10" t="str">
-        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$C91)</f>
+        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$C49)</f>
         <v/>
       </c>
       <c r="C116" s="9" t="str">
-        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$D91)</f>
+        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$D49)</f>
         <v/>
       </c>
       <c r="D116" s="9" t="str">
-        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$E91)</f>
+        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$E49)</f>
         <v/>
       </c>
       <c r="E116" s="11" t="str">
-        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$F91)</f>
+        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$F49)</f>
         <v/>
       </c>
       <c r="F116" s="11" t="str">
-        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$G91)</f>
+        <f>IF(Introducere_interna!$B49="","",Introducere_interna!$G49)</f>
         <v/>
       </c>
     </row>
     <row r="117" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A117" s="9" t="str">
+        <f>IF(Introducere_interna!$B50="","",15)</f>
+        <v/>
+      </c>
+      <c r="B117" s="10" t="str">
+        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$C50)</f>
+        <v/>
+      </c>
+      <c r="C117" s="9" t="str">
+        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$D50)</f>
+        <v/>
+      </c>
+      <c r="D117" s="9" t="str">
+        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$E50)</f>
+        <v/>
+      </c>
+      <c r="E117" s="11" t="str">
+        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$F50)</f>
+        <v/>
+      </c>
+      <c r="F117" s="11" t="str">
+        <f>IF(Introducere_interna!$B50="","",Introducere_interna!$G50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A118" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B118" s="34"/>
+      <c r="C118" s="34"/>
+      <c r="D118" s="34"/>
+      <c r="E118" s="34"/>
+      <c r="F118" s="12">
+        <f>SUM(F92:F117)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A120" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120" s="31"/>
+      <c r="C120" s="31"/>
+      <c r="D120" s="31"/>
+      <c r="E120" s="31"/>
+      <c r="F120" s="31"/>
+    </row>
+    <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A121" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A122" s="9" t="str">
+        <f>IF(Introducere_interna!$B51="","",1)</f>
+        <v/>
+      </c>
+      <c r="B122" s="10" t="str">
+        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$C51)</f>
+        <v/>
+      </c>
+      <c r="C122" s="9" t="str">
+        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$D51)</f>
+        <v/>
+      </c>
+      <c r="D122" s="9" t="str">
+        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$E51)</f>
+        <v/>
+      </c>
+      <c r="E122" s="11" t="str">
+        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$F51)</f>
+        <v/>
+      </c>
+      <c r="F122" s="11" t="str">
+        <f>IF(Introducere_interna!$B51="","",Introducere_interna!$G51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A123" s="9" t="str">
+        <f>IF(Introducere_interna!$B52="","",2)</f>
+        <v/>
+      </c>
+      <c r="B123" s="10" t="str">
+        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$C52)</f>
+        <v/>
+      </c>
+      <c r="C123" s="9" t="str">
+        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$D52)</f>
+        <v/>
+      </c>
+      <c r="D123" s="9" t="str">
+        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$E52)</f>
+        <v/>
+      </c>
+      <c r="E123" s="11" t="str">
+        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$F52)</f>
+        <v/>
+      </c>
+      <c r="F123" s="11" t="str">
+        <f>IF(Introducere_interna!$B52="","",Introducere_interna!$G52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A124" s="9"/>
+      <c r="B124" s="10"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+    </row>
+    <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A125" s="9"/>
+      <c r="B125" s="10"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="11"/>
+    </row>
+    <row r="126" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A126" s="9"/>
+      <c r="B126" s="10"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="11"/>
+    </row>
+    <row r="127" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A127" s="9"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+    </row>
+    <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A128" s="9"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+    </row>
+    <row r="129" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A129" s="9"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+    </row>
+    <row r="130" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A130" s="9"/>
+      <c r="B130" s="10"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+    </row>
+    <row r="131" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A131" s="9"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="11"/>
+    </row>
+    <row r="132" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A132" s="9"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+    </row>
+    <row r="133" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A133" s="9"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+    </row>
+    <row r="134" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A134" s="9" t="str">
+        <f>IF(Introducere_interna!$B53="","",3)</f>
+        <v/>
+      </c>
+      <c r="B134" s="10" t="str">
+        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$C53)</f>
+        <v/>
+      </c>
+      <c r="C134" s="9" t="str">
+        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$D53)</f>
+        <v/>
+      </c>
+      <c r="D134" s="9" t="str">
+        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$E53)</f>
+        <v/>
+      </c>
+      <c r="E134" s="11" t="str">
+        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$F53)</f>
+        <v/>
+      </c>
+      <c r="F134" s="11" t="str">
+        <f>IF(Introducere_interna!$B53="","",Introducere_interna!$G53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A135" s="9" t="str">
+        <f>IF(Introducere_interna!$B54="","",4)</f>
+        <v/>
+      </c>
+      <c r="B135" s="10" t="str">
+        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$C54)</f>
+        <v/>
+      </c>
+      <c r="C135" s="9" t="str">
+        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$D54)</f>
+        <v/>
+      </c>
+      <c r="D135" s="9" t="str">
+        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$E54)</f>
+        <v/>
+      </c>
+      <c r="E135" s="11" t="str">
+        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$F54)</f>
+        <v/>
+      </c>
+      <c r="F135" s="11" t="str">
+        <f>IF(Introducere_interna!$B54="","",Introducere_interna!$G54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A136" s="9" t="str">
+        <f>IF(Introducere_interna!$B55="","",5)</f>
+        <v/>
+      </c>
+      <c r="B136" s="10" t="str">
+        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$C55)</f>
+        <v/>
+      </c>
+      <c r="C136" s="9" t="str">
+        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$D55)</f>
+        <v/>
+      </c>
+      <c r="D136" s="9" t="str">
+        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$E55)</f>
+        <v/>
+      </c>
+      <c r="E136" s="11" t="str">
+        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$F55)</f>
+        <v/>
+      </c>
+      <c r="F136" s="11" t="str">
+        <f>IF(Introducere_interna!$B55="","",Introducere_interna!$G55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A137" s="9" t="str">
+        <f>IF(Introducere_interna!$B56="","",6)</f>
+        <v/>
+      </c>
+      <c r="B137" s="10" t="str">
+        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$C56)</f>
+        <v/>
+      </c>
+      <c r="C137" s="9" t="str">
+        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$D56)</f>
+        <v/>
+      </c>
+      <c r="D137" s="9" t="str">
+        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$E56)</f>
+        <v/>
+      </c>
+      <c r="E137" s="11" t="str">
+        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$F56)</f>
+        <v/>
+      </c>
+      <c r="F137" s="11" t="str">
+        <f>IF(Introducere_interna!$B56="","",Introducere_interna!$G56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A138" s="9" t="str">
+        <f>IF(Introducere_interna!$B57="","",7)</f>
+        <v/>
+      </c>
+      <c r="B138" s="10" t="str">
+        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$C57)</f>
+        <v/>
+      </c>
+      <c r="C138" s="9" t="str">
+        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$D57)</f>
+        <v/>
+      </c>
+      <c r="D138" s="9" t="str">
+        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$E57)</f>
+        <v/>
+      </c>
+      <c r="E138" s="11" t="str">
+        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$F57)</f>
+        <v/>
+      </c>
+      <c r="F138" s="11" t="str">
+        <f>IF(Introducere_interna!$B57="","",Introducere_interna!$G57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A139" s="9" t="str">
+        <f>IF(Introducere_interna!$B58="","",8)</f>
+        <v/>
+      </c>
+      <c r="B139" s="10" t="str">
+        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$C58)</f>
+        <v/>
+      </c>
+      <c r="C139" s="9" t="str">
+        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$D58)</f>
+        <v/>
+      </c>
+      <c r="D139" s="9" t="str">
+        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$E58)</f>
+        <v/>
+      </c>
+      <c r="E139" s="11" t="str">
+        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$F58)</f>
+        <v/>
+      </c>
+      <c r="F139" s="11" t="str">
+        <f>IF(Introducere_interna!$B58="","",Introducere_interna!$G58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A140" s="9" t="str">
+        <f>IF(Introducere_interna!$B59="","",9)</f>
+        <v/>
+      </c>
+      <c r="B140" s="10" t="str">
+        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$C59)</f>
+        <v/>
+      </c>
+      <c r="C140" s="9" t="str">
+        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$D59)</f>
+        <v/>
+      </c>
+      <c r="D140" s="9" t="str">
+        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$E59)</f>
+        <v/>
+      </c>
+      <c r="E140" s="11" t="str">
+        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$F59)</f>
+        <v/>
+      </c>
+      <c r="F140" s="11" t="str">
+        <f>IF(Introducere_interna!$B59="","",Introducere_interna!$G59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A141" s="9" t="str">
+        <f>IF(Introducere_interna!$B60="","",10)</f>
+        <v/>
+      </c>
+      <c r="B141" s="10" t="str">
+        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$C60)</f>
+        <v/>
+      </c>
+      <c r="C141" s="9" t="str">
+        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$D60)</f>
+        <v/>
+      </c>
+      <c r="D141" s="9" t="str">
+        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$E60)</f>
+        <v/>
+      </c>
+      <c r="E141" s="11" t="str">
+        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$F60)</f>
+        <v/>
+      </c>
+      <c r="F141" s="11" t="str">
+        <f>IF(Introducere_interna!$B60="","",Introducere_interna!$G60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A142" s="9" t="str">
+        <f>IF(Introducere_interna!$B61="","",11)</f>
+        <v/>
+      </c>
+      <c r="B142" s="10" t="str">
+        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$C61)</f>
+        <v/>
+      </c>
+      <c r="C142" s="9" t="str">
+        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$D61)</f>
+        <v/>
+      </c>
+      <c r="D142" s="9" t="str">
+        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$E61)</f>
+        <v/>
+      </c>
+      <c r="E142" s="11" t="str">
+        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$F61)</f>
+        <v/>
+      </c>
+      <c r="F142" s="11" t="str">
+        <f>IF(Introducere_interna!$B61="","",Introducere_interna!$G61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A143" s="9" t="str">
+        <f>IF(Introducere_interna!$B62="","",12)</f>
+        <v/>
+      </c>
+      <c r="B143" s="10" t="str">
+        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$C62)</f>
+        <v/>
+      </c>
+      <c r="C143" s="9" t="str">
+        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$D62)</f>
+        <v/>
+      </c>
+      <c r="D143" s="9" t="str">
+        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$E62)</f>
+        <v/>
+      </c>
+      <c r="E143" s="11" t="str">
+        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$F62)</f>
+        <v/>
+      </c>
+      <c r="F143" s="11" t="str">
+        <f>IF(Introducere_interna!$B62="","",Introducere_interna!$G62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A144" s="9" t="str">
+        <f>IF(Introducere_interna!$B63="","",13)</f>
+        <v/>
+      </c>
+      <c r="B144" s="10" t="str">
+        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$C63)</f>
+        <v/>
+      </c>
+      <c r="C144" s="9" t="str">
+        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$D63)</f>
+        <v/>
+      </c>
+      <c r="D144" s="9" t="str">
+        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$E63)</f>
+        <v/>
+      </c>
+      <c r="E144" s="11" t="str">
+        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$F63)</f>
+        <v/>
+      </c>
+      <c r="F144" s="11" t="str">
+        <f>IF(Introducere_interna!$B63="","",Introducere_interna!$G63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A145" s="9" t="str">
+        <f>IF(Introducere_interna!$B64="","",14)</f>
+        <v/>
+      </c>
+      <c r="B145" s="10" t="str">
+        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$C64)</f>
+        <v/>
+      </c>
+      <c r="C145" s="9" t="str">
+        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$D64)</f>
+        <v/>
+      </c>
+      <c r="D145" s="9" t="str">
+        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$E64)</f>
+        <v/>
+      </c>
+      <c r="E145" s="11" t="str">
+        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$F64)</f>
+        <v/>
+      </c>
+      <c r="F145" s="11" t="str">
+        <f>IF(Introducere_interna!$B64="","",Introducere_interna!$G64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A146" s="9" t="str">
+        <f>IF(Introducere_interna!$B65="","",15)</f>
+        <v/>
+      </c>
+      <c r="B146" s="10" t="str">
+        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$C65)</f>
+        <v/>
+      </c>
+      <c r="C146" s="9" t="str">
+        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$D65)</f>
+        <v/>
+      </c>
+      <c r="D146" s="9" t="str">
+        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$E65)</f>
+        <v/>
+      </c>
+      <c r="E146" s="11" t="str">
+        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$F65)</f>
+        <v/>
+      </c>
+      <c r="F146" s="11" t="str">
+        <f>IF(Introducere_interna!$B65="","",Introducere_interna!$G65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A147" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B147" s="34"/>
+      <c r="C147" s="34"/>
+      <c r="D147" s="34"/>
+      <c r="E147" s="34"/>
+      <c r="F147" s="12">
+        <f>SUM(F122:F146)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+    </row>
+    <row r="149" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A149" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B149" s="31"/>
+      <c r="C149" s="31"/>
+      <c r="D149" s="31"/>
+      <c r="E149" s="31"/>
+      <c r="F149" s="31"/>
+    </row>
+    <row r="150" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A150" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A151" s="9" t="str">
+        <f>IF(Introducere_interna!$B66="","",1)</f>
+        <v/>
+      </c>
+      <c r="B151" s="10" t="str">
+        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$C66)</f>
+        <v/>
+      </c>
+      <c r="C151" s="9" t="str">
+        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$D66)</f>
+        <v/>
+      </c>
+      <c r="D151" s="9" t="str">
+        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$E66)</f>
+        <v/>
+      </c>
+      <c r="E151" s="11" t="str">
+        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$F66)</f>
+        <v/>
+      </c>
+      <c r="F151" s="11" t="str">
+        <f>IF(Introducere_interna!$B66="","",Introducere_interna!$G66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A152" s="9" t="str">
+        <f>IF(Introducere_interna!$B67="","",2)</f>
+        <v/>
+      </c>
+      <c r="B152" s="10" t="str">
+        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$C67)</f>
+        <v/>
+      </c>
+      <c r="C152" s="9" t="str">
+        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$D67)</f>
+        <v/>
+      </c>
+      <c r="D152" s="9" t="str">
+        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$E67)</f>
+        <v/>
+      </c>
+      <c r="E152" s="11" t="str">
+        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$F67)</f>
+        <v/>
+      </c>
+      <c r="F152" s="11" t="str">
+        <f>IF(Introducere_interna!$B67="","",Introducere_interna!$G67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A153" s="9"/>
+      <c r="B153" s="10"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="11"/>
+    </row>
+    <row r="154" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A154" s="9"/>
+      <c r="B154" s="10"/>
+      <c r="C154" s="9"/>
+      <c r="D154" s="9"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="11"/>
+    </row>
+    <row r="155" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A155" s="9"/>
+      <c r="B155" s="10"/>
+      <c r="C155" s="9"/>
+      <c r="D155" s="9"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="11"/>
+    </row>
+    <row r="156" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A156" s="9"/>
+      <c r="B156" s="10"/>
+      <c r="C156" s="9"/>
+      <c r="D156" s="9"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+    </row>
+    <row r="157" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A157" s="9"/>
+      <c r="B157" s="10"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="9"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+    </row>
+    <row r="158" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A158" s="9"/>
+      <c r="B158" s="10"/>
+      <c r="C158" s="9"/>
+      <c r="D158" s="9"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="11"/>
+    </row>
+    <row r="159" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A159" s="9"/>
+      <c r="B159" s="10"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="9"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="11"/>
+    </row>
+    <row r="160" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A160" s="9"/>
+      <c r="B160" s="10"/>
+      <c r="C160" s="9"/>
+      <c r="D160" s="9"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
+    </row>
+    <row r="161" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A161" s="9"/>
+      <c r="B161" s="10"/>
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="11"/>
+    </row>
+    <row r="162" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A162" s="9"/>
+      <c r="B162" s="10"/>
+      <c r="C162" s="9"/>
+      <c r="D162" s="9"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="11"/>
+    </row>
+    <row r="163" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A163" s="9"/>
+      <c r="B163" s="10"/>
+      <c r="C163" s="9"/>
+      <c r="D163" s="9"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+    </row>
+    <row r="164" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A164" s="9"/>
+      <c r="B164" s="10"/>
+      <c r="C164" s="9"/>
+      <c r="D164" s="9"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="11"/>
+    </row>
+    <row r="165" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A165" s="9"/>
+      <c r="B165" s="10"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="11"/>
+    </row>
+    <row r="166" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A166" s="9"/>
+      <c r="B166" s="10"/>
+      <c r="C166" s="9"/>
+      <c r="D166" s="9"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="11"/>
+    </row>
+    <row r="167" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A167" s="9"/>
+      <c r="B167" s="10"/>
+      <c r="C167" s="9"/>
+      <c r="D167" s="9"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="11"/>
+    </row>
+    <row r="168" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A168" s="9"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="9"/>
+      <c r="D168" s="9"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="11"/>
+    </row>
+    <row r="169" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A169" s="9"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="9"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="11"/>
+    </row>
+    <row r="170" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A170" s="9"/>
+      <c r="B170" s="10"/>
+      <c r="C170" s="9"/>
+      <c r="D170" s="9"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="11"/>
+    </row>
+    <row r="171" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A171" s="9"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="11"/>
+    </row>
+    <row r="172" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A172" s="9"/>
+      <c r="B172" s="10"/>
+      <c r="C172" s="9"/>
+      <c r="D172" s="9"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="11"/>
+    </row>
+    <row r="173" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A173" s="9" t="str">
+        <f>IF(Introducere_interna!$B68="","",3)</f>
+        <v/>
+      </c>
+      <c r="B173" s="10" t="str">
+        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$C68)</f>
+        <v/>
+      </c>
+      <c r="C173" s="9" t="str">
+        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$D68)</f>
+        <v/>
+      </c>
+      <c r="D173" s="9" t="str">
+        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$E68)</f>
+        <v/>
+      </c>
+      <c r="E173" s="11" t="str">
+        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$F68)</f>
+        <v/>
+      </c>
+      <c r="F173" s="11" t="str">
+        <f>IF(Introducere_interna!$B68="","",Introducere_interna!$G68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A174" s="9" t="str">
+        <f>IF(Introducere_interna!$B69="","",4)</f>
+        <v/>
+      </c>
+      <c r="B174" s="10" t="str">
+        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$C69)</f>
+        <v/>
+      </c>
+      <c r="C174" s="9" t="str">
+        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$D69)</f>
+        <v/>
+      </c>
+      <c r="D174" s="9" t="str">
+        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$E69)</f>
+        <v/>
+      </c>
+      <c r="E174" s="11" t="str">
+        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$F69)</f>
+        <v/>
+      </c>
+      <c r="F174" s="11" t="str">
+        <f>IF(Introducere_interna!$B69="","",Introducere_interna!$G69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A175" s="9" t="str">
+        <f>IF(Introducere_interna!$B70="","",5)</f>
+        <v/>
+      </c>
+      <c r="B175" s="10" t="str">
+        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$C70)</f>
+        <v/>
+      </c>
+      <c r="C175" s="9" t="str">
+        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$D70)</f>
+        <v/>
+      </c>
+      <c r="D175" s="9" t="str">
+        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$E70)</f>
+        <v/>
+      </c>
+      <c r="E175" s="11" t="str">
+        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$F70)</f>
+        <v/>
+      </c>
+      <c r="F175" s="11" t="str">
+        <f>IF(Introducere_interna!$B70="","",Introducere_interna!$G70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A176" s="9" t="str">
+        <f>IF(Introducere_interna!$B71="","",6)</f>
+        <v/>
+      </c>
+      <c r="B176" s="10" t="str">
+        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$C71)</f>
+        <v/>
+      </c>
+      <c r="C176" s="9" t="str">
+        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$D71)</f>
+        <v/>
+      </c>
+      <c r="D176" s="9" t="str">
+        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$E71)</f>
+        <v/>
+      </c>
+      <c r="E176" s="11" t="str">
+        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$F71)</f>
+        <v/>
+      </c>
+      <c r="F176" s="11" t="str">
+        <f>IF(Introducere_interna!$B71="","",Introducere_interna!$G71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A177" s="9" t="str">
+        <f>IF(Introducere_interna!$B72="","",7)</f>
+        <v/>
+      </c>
+      <c r="B177" s="10" t="str">
+        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$C72)</f>
+        <v/>
+      </c>
+      <c r="C177" s="9" t="str">
+        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$D72)</f>
+        <v/>
+      </c>
+      <c r="D177" s="9" t="str">
+        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$E72)</f>
+        <v/>
+      </c>
+      <c r="E177" s="11" t="str">
+        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$F72)</f>
+        <v/>
+      </c>
+      <c r="F177" s="11" t="str">
+        <f>IF(Introducere_interna!$B72="","",Introducere_interna!$G72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A178" s="9" t="str">
+        <f>IF(Introducere_interna!$B73="","",8)</f>
+        <v/>
+      </c>
+      <c r="B178" s="10" t="str">
+        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$C73)</f>
+        <v/>
+      </c>
+      <c r="C178" s="9" t="str">
+        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$D73)</f>
+        <v/>
+      </c>
+      <c r="D178" s="9" t="str">
+        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$E73)</f>
+        <v/>
+      </c>
+      <c r="E178" s="11" t="str">
+        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$F73)</f>
+        <v/>
+      </c>
+      <c r="F178" s="11" t="str">
+        <f>IF(Introducere_interna!$B73="","",Introducere_interna!$G73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A179" s="9" t="str">
+        <f>IF(Introducere_interna!$B74="","",9)</f>
+        <v/>
+      </c>
+      <c r="B179" s="10" t="str">
+        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$C74)</f>
+        <v/>
+      </c>
+      <c r="C179" s="9" t="str">
+        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$D74)</f>
+        <v/>
+      </c>
+      <c r="D179" s="9" t="str">
+        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$E74)</f>
+        <v/>
+      </c>
+      <c r="E179" s="11" t="str">
+        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$F74)</f>
+        <v/>
+      </c>
+      <c r="F179" s="11" t="str">
+        <f>IF(Introducere_interna!$B74="","",Introducere_interna!$G74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A180" s="9" t="str">
+        <f>IF(Introducere_interna!$B75="","",10)</f>
+        <v/>
+      </c>
+      <c r="B180" s="10" t="str">
+        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$C75)</f>
+        <v/>
+      </c>
+      <c r="C180" s="9" t="str">
+        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$D75)</f>
+        <v/>
+      </c>
+      <c r="D180" s="9" t="str">
+        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$E75)</f>
+        <v/>
+      </c>
+      <c r="E180" s="11" t="str">
+        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$F75)</f>
+        <v/>
+      </c>
+      <c r="F180" s="11" t="str">
+        <f>IF(Introducere_interna!$B75="","",Introducere_interna!$G75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A181" s="9" t="str">
+        <f>IF(Introducere_interna!$B76="","",11)</f>
+        <v/>
+      </c>
+      <c r="B181" s="10" t="str">
+        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$C76)</f>
+        <v/>
+      </c>
+      <c r="C181" s="9" t="str">
+        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$D76)</f>
+        <v/>
+      </c>
+      <c r="D181" s="9" t="str">
+        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$E76)</f>
+        <v/>
+      </c>
+      <c r="E181" s="11" t="str">
+        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$F76)</f>
+        <v/>
+      </c>
+      <c r="F181" s="11" t="str">
+        <f>IF(Introducere_interna!$B76="","",Introducere_interna!$G76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A182" s="9" t="str">
+        <f>IF(Introducere_interna!$B77="","",12)</f>
+        <v/>
+      </c>
+      <c r="B182" s="10" t="str">
+        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$C77)</f>
+        <v/>
+      </c>
+      <c r="C182" s="9" t="str">
+        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$D77)</f>
+        <v/>
+      </c>
+      <c r="D182" s="9" t="str">
+        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$E77)</f>
+        <v/>
+      </c>
+      <c r="E182" s="11" t="str">
+        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$F77)</f>
+        <v/>
+      </c>
+      <c r="F182" s="11" t="str">
+        <f>IF(Introducere_interna!$B77="","",Introducere_interna!$G77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A183" s="9" t="str">
+        <f>IF(Introducere_interna!$B78="","",13)</f>
+        <v/>
+      </c>
+      <c r="B183" s="10" t="str">
+        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$C78)</f>
+        <v/>
+      </c>
+      <c r="C183" s="9" t="str">
+        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$D78)</f>
+        <v/>
+      </c>
+      <c r="D183" s="9" t="str">
+        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$E78)</f>
+        <v/>
+      </c>
+      <c r="E183" s="11" t="str">
+        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$F78)</f>
+        <v/>
+      </c>
+      <c r="F183" s="11" t="str">
+        <f>IF(Introducere_interna!$B78="","",Introducere_interna!$G78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A184" s="9" t="str">
+        <f>IF(Introducere_interna!$B79="","",14)</f>
+        <v/>
+      </c>
+      <c r="B184" s="10" t="str">
+        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$C79)</f>
+        <v/>
+      </c>
+      <c r="C184" s="9" t="str">
+        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$D79)</f>
+        <v/>
+      </c>
+      <c r="D184" s="9" t="str">
+        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$E79)</f>
+        <v/>
+      </c>
+      <c r="E184" s="11" t="str">
+        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$F79)</f>
+        <v/>
+      </c>
+      <c r="F184" s="11" t="str">
+        <f>IF(Introducere_interna!$B79="","",Introducere_interna!$G79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A185" s="9" t="str">
+        <f>IF(Introducere_interna!$B80="","",15)</f>
+        <v/>
+      </c>
+      <c r="B185" s="10" t="str">
+        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$C80)</f>
+        <v/>
+      </c>
+      <c r="C185" s="9" t="str">
+        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$D80)</f>
+        <v/>
+      </c>
+      <c r="D185" s="9" t="str">
+        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$E80)</f>
+        <v/>
+      </c>
+      <c r="E185" s="11" t="str">
+        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$F80)</f>
+        <v/>
+      </c>
+      <c r="F185" s="11" t="str">
+        <f>IF(Introducere_interna!$B80="","",Introducere_interna!$G80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A186" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B186" s="34"/>
+      <c r="C186" s="34"/>
+      <c r="D186" s="34"/>
+      <c r="E186" s="34"/>
+      <c r="F186" s="12">
+        <f>SUM(F151:F185)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+    </row>
+    <row r="188" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A188" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B188" s="31"/>
+      <c r="C188" s="31"/>
+      <c r="D188" s="31"/>
+      <c r="E188" s="31"/>
+      <c r="F188" s="31"/>
+    </row>
+    <row r="189" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A189" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A190" s="9" t="str">
+        <f>IF(Introducere_interna!$B81="","",1)</f>
+        <v/>
+      </c>
+      <c r="B190" s="10" t="str">
+        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$C81)</f>
+        <v/>
+      </c>
+      <c r="C190" s="9" t="str">
+        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$D81)</f>
+        <v/>
+      </c>
+      <c r="D190" s="9" t="str">
+        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$E81)</f>
+        <v/>
+      </c>
+      <c r="E190" s="11" t="str">
+        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$F81)</f>
+        <v/>
+      </c>
+      <c r="F190" s="11" t="str">
+        <f>IF(Introducere_interna!$B81="","",Introducere_interna!$G81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A191" s="9" t="str">
+        <f>IF(Introducere_interna!$B82="","",2)</f>
+        <v/>
+      </c>
+      <c r="B191" s="10" t="str">
+        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$C82)</f>
+        <v/>
+      </c>
+      <c r="C191" s="9" t="str">
+        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$D82)</f>
+        <v/>
+      </c>
+      <c r="D191" s="9" t="str">
+        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$E82)</f>
+        <v/>
+      </c>
+      <c r="E191" s="11" t="str">
+        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$F82)</f>
+        <v/>
+      </c>
+      <c r="F191" s="11" t="str">
+        <f>IF(Introducere_interna!$B82="","",Introducere_interna!$G82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A192" s="9" t="str">
+        <f>IF(Introducere_interna!$B83="","",3)</f>
+        <v/>
+      </c>
+      <c r="B192" s="10" t="str">
+        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$C83)</f>
+        <v/>
+      </c>
+      <c r="C192" s="9" t="str">
+        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$D83)</f>
+        <v/>
+      </c>
+      <c r="D192" s="9" t="str">
+        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$E83)</f>
+        <v/>
+      </c>
+      <c r="E192" s="11" t="str">
+        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$F83)</f>
+        <v/>
+      </c>
+      <c r="F192" s="11" t="str">
+        <f>IF(Introducere_interna!$B83="","",Introducere_interna!$G83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A193" s="9" t="str">
+        <f>IF(Introducere_interna!$B84="","",4)</f>
+        <v/>
+      </c>
+      <c r="B193" s="10" t="str">
+        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$C84)</f>
+        <v/>
+      </c>
+      <c r="C193" s="9" t="str">
+        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$D84)</f>
+        <v/>
+      </c>
+      <c r="D193" s="9" t="str">
+        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$E84)</f>
+        <v/>
+      </c>
+      <c r="E193" s="11" t="str">
+        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$F84)</f>
+        <v/>
+      </c>
+      <c r="F193" s="11" t="str">
+        <f>IF(Introducere_interna!$B84="","",Introducere_interna!$G84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A194" s="9" t="str">
+        <f>IF(Introducere_interna!$B85="","",5)</f>
+        <v/>
+      </c>
+      <c r="B194" s="10" t="str">
+        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$C85)</f>
+        <v/>
+      </c>
+      <c r="C194" s="9" t="str">
+        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$D85)</f>
+        <v/>
+      </c>
+      <c r="D194" s="9" t="str">
+        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$E85)</f>
+        <v/>
+      </c>
+      <c r="E194" s="11" t="str">
+        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$F85)</f>
+        <v/>
+      </c>
+      <c r="F194" s="11" t="str">
+        <f>IF(Introducere_interna!$B85="","",Introducere_interna!$G85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A195" s="9" t="str">
+        <f>IF(Introducere_interna!$B86="","",6)</f>
+        <v/>
+      </c>
+      <c r="B195" s="10" t="str">
+        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$C86)</f>
+        <v/>
+      </c>
+      <c r="C195" s="9" t="str">
+        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$D86)</f>
+        <v/>
+      </c>
+      <c r="D195" s="9" t="str">
+        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$E86)</f>
+        <v/>
+      </c>
+      <c r="E195" s="11" t="str">
+        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$F86)</f>
+        <v/>
+      </c>
+      <c r="F195" s="11" t="str">
+        <f>IF(Introducere_interna!$B86="","",Introducere_interna!$G86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A196" s="9" t="str">
+        <f>IF(Introducere_interna!$B87="","",7)</f>
+        <v/>
+      </c>
+      <c r="B196" s="10" t="str">
+        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$C87)</f>
+        <v/>
+      </c>
+      <c r="C196" s="9" t="str">
+        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$D87)</f>
+        <v/>
+      </c>
+      <c r="D196" s="9" t="str">
+        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$E87)</f>
+        <v/>
+      </c>
+      <c r="E196" s="11" t="str">
+        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$F87)</f>
+        <v/>
+      </c>
+      <c r="F196" s="11" t="str">
+        <f>IF(Introducere_interna!$B87="","",Introducere_interna!$G87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A197" s="9" t="str">
+        <f>IF(Introducere_interna!$B88="","",8)</f>
+        <v/>
+      </c>
+      <c r="B197" s="10" t="str">
+        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$C88)</f>
+        <v/>
+      </c>
+      <c r="C197" s="9" t="str">
+        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$D88)</f>
+        <v/>
+      </c>
+      <c r="D197" s="9" t="str">
+        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$E88)</f>
+        <v/>
+      </c>
+      <c r="E197" s="11" t="str">
+        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$F88)</f>
+        <v/>
+      </c>
+      <c r="F197" s="11" t="str">
+        <f>IF(Introducere_interna!$B88="","",Introducere_interna!$G88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A198" s="9" t="str">
+        <f>IF(Introducere_interna!$B89="","",9)</f>
+        <v/>
+      </c>
+      <c r="B198" s="10" t="str">
+        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$C89)</f>
+        <v/>
+      </c>
+      <c r="C198" s="9" t="str">
+        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$D89)</f>
+        <v/>
+      </c>
+      <c r="D198" s="9" t="str">
+        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$E89)</f>
+        <v/>
+      </c>
+      <c r="E198" s="11" t="str">
+        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$F89)</f>
+        <v/>
+      </c>
+      <c r="F198" s="11" t="str">
+        <f>IF(Introducere_interna!$B89="","",Introducere_interna!$G89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A199" s="9" t="str">
+        <f>IF(Introducere_interna!$B90="","",10)</f>
+        <v/>
+      </c>
+      <c r="B199" s="10" t="str">
+        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$C90)</f>
+        <v/>
+      </c>
+      <c r="C199" s="9" t="str">
+        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$D90)</f>
+        <v/>
+      </c>
+      <c r="D199" s="9" t="str">
+        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$E90)</f>
+        <v/>
+      </c>
+      <c r="E199" s="11" t="str">
+        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$F90)</f>
+        <v/>
+      </c>
+      <c r="F199" s="11" t="str">
+        <f>IF(Introducere_interna!$B90="","",Introducere_interna!$G90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A200" s="9" t="str">
+        <f>IF(Introducere_interna!$B91="","",11)</f>
+        <v/>
+      </c>
+      <c r="B200" s="10" t="str">
+        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$C91)</f>
+        <v/>
+      </c>
+      <c r="C200" s="9" t="str">
+        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$D91)</f>
+        <v/>
+      </c>
+      <c r="D200" s="9" t="str">
+        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$E91)</f>
+        <v/>
+      </c>
+      <c r="E200" s="11" t="str">
+        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$F91)</f>
+        <v/>
+      </c>
+      <c r="F200" s="11" t="str">
+        <f>IF(Introducere_interna!$B91="","",Introducere_interna!$G91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A201" s="9" t="str">
         <f>IF(Introducere_interna!$B92="","",12)</f>
         <v/>
       </c>
-      <c r="B117" s="10" t="str">
+      <c r="B201" s="10" t="str">
         <f>IF(Introducere_interna!$B92="","",Introducere_interna!$C92)</f>
         <v/>
       </c>
-      <c r="C117" s="9" t="str">
+      <c r="C201" s="9" t="str">
         <f>IF(Introducere_interna!$B92="","",Introducere_interna!$D92)</f>
         <v/>
       </c>
-      <c r="D117" s="9" t="str">
+      <c r="D201" s="9" t="str">
         <f>IF(Introducere_interna!$B92="","",Introducere_interna!$E92)</f>
         <v/>
       </c>
-      <c r="E117" s="11" t="str">
+      <c r="E201" s="11" t="str">
         <f>IF(Introducere_interna!$B92="","",Introducere_interna!$F92)</f>
         <v/>
       </c>
-      <c r="F117" s="11" t="str">
+      <c r="F201" s="11" t="str">
         <f>IF(Introducere_interna!$B92="","",Introducere_interna!$G92)</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="9" t="str">
+    <row r="202" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A202" s="9" t="str">
         <f>IF(Introducere_interna!$B93="","",13)</f>
         <v/>
       </c>
-      <c r="B118" s="10" t="str">
+      <c r="B202" s="10" t="str">
         <f>IF(Introducere_interna!$B93="","",Introducere_interna!$C93)</f>
         <v/>
       </c>
-      <c r="C118" s="9" t="str">
+      <c r="C202" s="9" t="str">
         <f>IF(Introducere_interna!$B93="","",Introducere_interna!$D93)</f>
         <v/>
       </c>
-      <c r="D118" s="9" t="str">
+      <c r="D202" s="9" t="str">
         <f>IF(Introducere_interna!$B93="","",Introducere_interna!$E93)</f>
         <v/>
       </c>
-      <c r="E118" s="11" t="str">
+      <c r="E202" s="11" t="str">
         <f>IF(Introducere_interna!$B93="","",Introducere_interna!$F93)</f>
         <v/>
       </c>
-      <c r="F118" s="11" t="str">
+      <c r="F202" s="11" t="str">
         <f>IF(Introducere_interna!$B93="","",Introducere_interna!$G93)</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="9" t="str">
+    <row r="203" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A203" s="9" t="str">
         <f>IF(Introducere_interna!$B94="","",14)</f>
         <v/>
       </c>
-      <c r="B119" s="10" t="str">
+      <c r="B203" s="10" t="str">
         <f>IF(Introducere_interna!$B94="","",Introducere_interna!$C94)</f>
         <v/>
       </c>
-      <c r="C119" s="9" t="str">
+      <c r="C203" s="9" t="str">
         <f>IF(Introducere_interna!$B94="","",Introducere_interna!$D94)</f>
         <v/>
       </c>
-      <c r="D119" s="9" t="str">
+      <c r="D203" s="9" t="str">
         <f>IF(Introducere_interna!$B94="","",Introducere_interna!$E94)</f>
         <v/>
       </c>
-      <c r="E119" s="11" t="str">
+      <c r="E203" s="11" t="str">
         <f>IF(Introducere_interna!$B94="","",Introducere_interna!$F94)</f>
         <v/>
       </c>
-      <c r="F119" s="11" t="str">
+      <c r="F203" s="11" t="str">
         <f>IF(Introducere_interna!$B94="","",Introducere_interna!$G94)</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="9" t="str">
+    <row r="204" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A204" s="9" t="str">
         <f>IF(Introducere_interna!$B95="","",15)</f>
         <v/>
       </c>
-      <c r="B120" s="10" t="str">
+      <c r="B204" s="10" t="str">
         <f>IF(Introducere_interna!$B95="","",Introducere_interna!$C95)</f>
         <v/>
       </c>
-      <c r="C120" s="9" t="str">
+      <c r="C204" s="9" t="str">
         <f>IF(Introducere_interna!$B95="","",Introducere_interna!$D95)</f>
         <v/>
       </c>
-      <c r="D120" s="9" t="str">
+      <c r="D204" s="9" t="str">
         <f>IF(Introducere_interna!$B95="","",Introducere_interna!$E95)</f>
         <v/>
       </c>
-      <c r="E120" s="11" t="str">
+      <c r="E204" s="11" t="str">
         <f>IF(Introducere_interna!$B95="","",Introducere_interna!$F95)</f>
         <v/>
       </c>
-      <c r="F120" s="11" t="str">
+      <c r="F204" s="11" t="str">
         <f>IF(Introducere_interna!$B95="","",Introducere_interna!$G95)</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="32" t="s">
+    <row r="205" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A205" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="33"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="33"/>
-      <c r="E121" s="33"/>
-      <c r="F121" s="12">
-        <f>SUM(F106:F120)</f>
+      <c r="B205" s="34"/>
+      <c r="C205" s="34"/>
+      <c r="D205" s="34"/>
+      <c r="E205" s="34"/>
+      <c r="F205" s="12">
+        <f>SUM(F190:F204)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-    </row>
-    <row r="123" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="39" t="s">
+    <row r="206" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+    </row>
+    <row r="207" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A207" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B123" s="31"/>
-      <c r="C123" s="31"/>
-      <c r="D123" s="31"/>
-      <c r="E123" s="31"/>
-      <c r="F123" s="13">
-        <f>SUM(F26,F45,F64,F83,F102,F121)</f>
-        <v>191570.625</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="39" t="s">
+      <c r="B207" s="31"/>
+      <c r="C207" s="31"/>
+      <c r="D207" s="31"/>
+      <c r="E207" s="31"/>
+      <c r="F207" s="13">
+        <f>SUM(F51,F88,F118,F147,F186,F205)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A208" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B124" s="31"/>
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="31"/>
-      <c r="F124" s="13">
-        <f>F123*Setari!$B$2</f>
-        <v>38314.125</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="37" t="s">
+      <c r="B208" s="31"/>
+      <c r="C208" s="31"/>
+      <c r="D208" s="31"/>
+      <c r="E208" s="31"/>
+      <c r="F208" s="13">
+        <f>F207*Setari!$B$2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A209" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B125" s="38"/>
-      <c r="C125" s="38"/>
-      <c r="D125" s="38"/>
-      <c r="E125" s="38"/>
-      <c r="F125" s="14">
-        <f>F123+F124</f>
-        <v>229884.75</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-    </row>
-    <row r="127" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-    </row>
-    <row r="128" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="40" t="s">
+      <c r="B209" s="36"/>
+      <c r="C209" s="36"/>
+      <c r="D209" s="36"/>
+      <c r="E209" s="36"/>
+      <c r="F209" s="14">
+        <f>F207+F208</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+    </row>
+    <row r="211" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+      <c r="F211" s="1"/>
+    </row>
+    <row r="212" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A212" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B128" s="31"/>
-      <c r="C128" s="31"/>
-      <c r="D128" s="31"/>
-      <c r="E128" s="31"/>
-      <c r="F128" s="31"/>
-    </row>
-    <row r="129" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="15" t="s">
+      <c r="B212" s="31"/>
+      <c r="C212" s="31"/>
+      <c r="D212" s="31"/>
+      <c r="E212" s="31"/>
+      <c r="F212" s="31"/>
+    </row>
+    <row r="213" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A213" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B129" s="35" t="s">
+      <c r="B213" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C129" s="31"/>
-      <c r="D129" s="31"/>
-      <c r="E129" s="31"/>
-      <c r="F129" s="31"/>
-    </row>
-    <row r="130" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="15" t="s">
+      <c r="C213" s="31"/>
+      <c r="D213" s="31"/>
+      <c r="E213" s="31"/>
+      <c r="F213" s="31"/>
+    </row>
+    <row r="214" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A214" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="35" t="s">
+      <c r="B214" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C130" s="31"/>
-      <c r="D130" s="31"/>
-      <c r="E130" s="31"/>
-      <c r="F130" s="31"/>
-    </row>
-    <row r="131" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="15" t="s">
+      <c r="C214" s="31"/>
+      <c r="D214" s="31"/>
+      <c r="E214" s="31"/>
+      <c r="F214" s="31"/>
+    </row>
+    <row r="215" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A215" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B131" s="35" t="s">
+      <c r="B215" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C131" s="31"/>
-      <c r="D131" s="31"/>
-      <c r="E131" s="31"/>
-      <c r="F131" s="31"/>
-    </row>
-    <row r="132" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="15" t="s">
+      <c r="C215" s="31"/>
+      <c r="D215" s="31"/>
+      <c r="E215" s="31"/>
+      <c r="F215" s="31"/>
+    </row>
+    <row r="216" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A216" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B132" s="35" t="s">
+      <c r="B216" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C132" s="31"/>
-      <c r="D132" s="31"/>
-      <c r="E132" s="31"/>
-      <c r="F132" s="31"/>
-    </row>
-    <row r="133" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
+      <c r="C216" s="31"/>
+      <c r="D216" s="31"/>
+      <c r="E216" s="31"/>
+      <c r="F216" s="31"/>
+    </row>
+    <row r="217" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+      <c r="E217" s="1"/>
+      <c r="F217" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A205:E205"/>
+    <mergeCell ref="A186:E186"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="B216:F216"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A209:E209"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A207:E207"/>
+    <mergeCell ref="B215:F215"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A208:E208"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="A212:F212"/>
+    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="A118:E118"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
@@ -6093,7 +6495,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="39" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="41"/>
